--- a/hospital/стены/hospital-walls.xlsx
+++ b/hospital/стены/hospital-walls.xlsx
@@ -4,36 +4,38 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" codeName="ЭтаКнига" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="898" firstSheet="7" activeTab="7"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="898" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2.6шт" sheetId="20" r:id="rId1"/>
-    <sheet name="2.5шт" sheetId="19" r:id="rId2"/>
-    <sheet name="Общ" sheetId="18" r:id="rId3"/>
-    <sheet name="2.4ГВЛ" sheetId="17" r:id="rId4"/>
-    <sheet name="черновик 1-5" sheetId="16" r:id="rId5"/>
-    <sheet name="общий" sheetId="1" r:id="rId6"/>
-    <sheet name="4.1шпИнв" sheetId="15" r:id="rId7"/>
-    <sheet name="3.3ГВЛинв" sheetId="22" r:id="rId8"/>
-    <sheet name="3.2штИнв" sheetId="21" r:id="rId9"/>
-    <sheet name="3.1штИнв" sheetId="14" r:id="rId10"/>
-    <sheet name="№1" sheetId="12" r:id="rId11"/>
-    <sheet name="№2" sheetId="13" r:id="rId12"/>
-    <sheet name="1.1.1" sheetId="9" r:id="rId13"/>
-    <sheet name="1.2.1" sheetId="2" r:id="rId14"/>
-    <sheet name="1.2.2" sheetId="3" r:id="rId15"/>
-    <sheet name="1.3.1" sheetId="4" r:id="rId16"/>
-    <sheet name="1.3.2" sheetId="7" r:id="rId17"/>
-    <sheet name="1.4.1" sheetId="6" r:id="rId18"/>
-    <sheet name="1.4.2" sheetId="10" r:id="rId19"/>
-    <sheet name="1.5.1" sheetId="8" r:id="rId20"/>
+    <sheet name="5.1Шлф" sheetId="24" r:id="rId1"/>
+    <sheet name="2.6шт" sheetId="20" r:id="rId2"/>
+    <sheet name="2.5шт" sheetId="19" r:id="rId3"/>
+    <sheet name="Общ" sheetId="18" r:id="rId4"/>
+    <sheet name="2.4ГВЛ" sheetId="17" r:id="rId5"/>
+    <sheet name="черновик 1-5" sheetId="16" r:id="rId6"/>
+    <sheet name="общий" sheetId="1" r:id="rId7"/>
+    <sheet name="4.1шпИнв" sheetId="15" r:id="rId8"/>
+    <sheet name="3.4ГВЛинв5э" sheetId="23" r:id="rId9"/>
+    <sheet name="3.3ГВЛинв" sheetId="22" r:id="rId10"/>
+    <sheet name="3.2штИнв" sheetId="21" r:id="rId11"/>
+    <sheet name="3.1штИнв" sheetId="14" r:id="rId12"/>
+    <sheet name="№1" sheetId="12" r:id="rId13"/>
+    <sheet name="№2" sheetId="13" r:id="rId14"/>
+    <sheet name="1.1.1" sheetId="9" r:id="rId15"/>
+    <sheet name="1.2.1" sheetId="2" r:id="rId16"/>
+    <sheet name="1.2.2" sheetId="3" r:id="rId17"/>
+    <sheet name="1.3.1" sheetId="4" r:id="rId18"/>
+    <sheet name="1.3.2" sheetId="7" r:id="rId19"/>
+    <sheet name="1.4.1" sheetId="6" r:id="rId20"/>
+    <sheet name="1.4.2" sheetId="10" r:id="rId21"/>
+    <sheet name="1.5.1" sheetId="8" r:id="rId22"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2486" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2536" uniqueCount="929">
   <si>
     <t>Указать название организации (на бланке организации)</t>
   </si>
@@ -2823,6 +2825,11 @@
   </si>
   <si>
     <t>Подвал</t>
+  </si>
+  <si>
+    <t>Шлифование бетонных поверхностей
+стен (снятие наплывов и швов, снятие
+цементного молочка)</t>
   </si>
 </sst>
 </file>
@@ -3284,7 +3291,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3548,6 +3555,18 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -3596,6 +3615,24 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3608,29 +3645,11 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3946,7 +3965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
@@ -3959,26 +3978,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="96" t="s">
         <v>814</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="65" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="97" t="s">
         <v>816</v>
       </c>
-      <c r="C2" s="94"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="83" t="s">
+      <c r="C2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="93" t="s">
         <v>758</v>
       </c>
       <c r="F2" s="67" t="s">
@@ -3988,74 +4007,126 @@
         <v>817</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="82">
+    <row r="3" spans="1:7" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="92">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="s">
-        <v>439</v>
-      </c>
-      <c r="C3" s="97"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="84" t="s">
-        <v>926</v>
-      </c>
-      <c r="F3" s="82" t="s">
+      <c r="B3" s="100" t="s">
+        <v>928</v>
+      </c>
+      <c r="C3" s="101"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="94" t="s">
+        <v>829</v>
+      </c>
+      <c r="F3" s="92" t="s">
         <v>46</v>
       </c>
       <c r="G3" s="70">
-        <f>B7</f>
-        <v>375.2</v>
+        <f>B11</f>
+        <v>4683.1000000000004</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="99"/>
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="103"/>
     </row>
     <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="82" t="s">
+      <c r="A5" s="92" t="s">
         <v>831</v>
       </c>
-      <c r="B5" s="82" t="s">
+      <c r="B5" s="92" t="s">
         <v>821</v>
       </c>
-      <c r="C5" s="100"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="82">
-        <v>-1</v>
+      <c r="A6" s="92">
+        <v>1</v>
       </c>
       <c r="B6" s="70">
-        <v>375.2</v>
-      </c>
-      <c r="C6" s="100"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="101"/>
+        <v>897.3</v>
+      </c>
+      <c r="C6" s="104"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="105"/>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="92">
+        <v>2</v>
+      </c>
+      <c r="B7" s="70">
+        <v>903.4</v>
+      </c>
+      <c r="C7" s="104"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="92">
+        <v>3</v>
+      </c>
+      <c r="B8" s="70">
+        <v>902.4</v>
+      </c>
+      <c r="C8" s="104"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="92">
+        <v>4</v>
+      </c>
+      <c r="B9" s="70">
+        <v>1001.4</v>
+      </c>
+      <c r="C9" s="104"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="92">
+        <v>5</v>
+      </c>
+      <c r="B10" s="70">
+        <v>978.6</v>
+      </c>
+      <c r="C10" s="104"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="95" t="s">
         <v>828</v>
       </c>
-      <c r="B7" s="70">
-        <f>SUM(B6:B6)</f>
-        <v>375.2</v>
-      </c>
-      <c r="C7" s="100"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="101"/>
+      <c r="B11" s="70">
+        <f>SUM(B6:B10)</f>
+        <v>4683.1000000000004</v>
+      </c>
+      <c r="C11" s="104"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4063,13 +4134,267 @@
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="C5:G7"/>
+    <mergeCell ref="C5:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="56.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>757</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>758</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="60" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.3">
+      <c r="A2" s="42">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>759</v>
+      </c>
+      <c r="E2" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="59">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="42">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="8">
+        <v>93.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="42">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="8">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="42">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="8">
+        <v>262.60000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="42">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="8">
+        <v>9.15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="54" x14ac:dyDescent="0.3">
+      <c r="A7" s="42">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="8">
+        <v>10.55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="42">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="8">
+        <v>9.0500000000000007</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="96" t="s">
+        <v>814</v>
+      </c>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+    </row>
+    <row r="2" spans="1:7" s="77" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="89" t="s">
+        <v>815</v>
+      </c>
+      <c r="B2" s="127" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2" s="129"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="91" t="s">
+        <v>758</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="67" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="89">
+        <v>1</v>
+      </c>
+      <c r="B3" s="100" t="s">
+        <v>439</v>
+      </c>
+      <c r="C3" s="101"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="90" t="s">
+        <v>927</v>
+      </c>
+      <c r="F3" s="89" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="70">
+        <v>2924.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист6"/>
   <dimension ref="A1:L72"/>
@@ -4085,25 +4410,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="96" t="s">
         <v>814</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
     </row>
     <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="65" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="97" t="s">
         <v>816</v>
       </c>
-      <c r="C2" s="94"/>
-      <c r="D2" s="95"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="99"/>
       <c r="E2" s="66" t="s">
         <v>758</v>
       </c>
@@ -4118,11 +4443,11 @@
       <c r="A3" s="68">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="100" t="s">
         <v>439</v>
       </c>
-      <c r="C3" s="97"/>
-      <c r="D3" s="98"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="102"/>
       <c r="E3" s="69" t="s">
         <v>829</v>
       </c>
@@ -4135,13 +4460,13 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="99"/>
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="103"/>
     </row>
     <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="68" t="s">
@@ -4150,11 +4475,11 @@
       <c r="B5" s="68" t="s">
         <v>821</v>
       </c>
-      <c r="C5" s="100"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
     </row>
     <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="68">
@@ -4163,11 +4488,11 @@
       <c r="B6" s="70">
         <v>752.48</v>
       </c>
-      <c r="C6" s="100"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="101"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="105"/>
     </row>
     <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="68">
@@ -4176,11 +4501,11 @@
       <c r="B7" s="70">
         <v>806</v>
       </c>
-      <c r="C7" s="100"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="101"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
     </row>
     <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="68">
@@ -4189,11 +4514,11 @@
       <c r="B8" s="70">
         <v>788.8</v>
       </c>
-      <c r="C8" s="100"/>
-      <c r="D8" s="101"/>
-      <c r="E8" s="101"/>
-      <c r="F8" s="101"/>
-      <c r="G8" s="101"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
     </row>
     <row r="9" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="68">
@@ -4202,11 +4527,11 @@
       <c r="B9" s="70">
         <v>788.8</v>
       </c>
-      <c r="C9" s="100"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
     </row>
     <row r="10" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="68">
@@ -4215,11 +4540,11 @@
       <c r="B10" s="70">
         <v>610.4</v>
       </c>
-      <c r="C10" s="100"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
-      <c r="F10" s="101"/>
-      <c r="G10" s="101"/>
+      <c r="C10" s="104"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
     </row>
     <row r="11" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="74" t="s">
@@ -4229,11 +4554,11 @@
         <f>SUM(B6:B10)</f>
         <v>3746.48</v>
       </c>
-      <c r="C11" s="100"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="101"/>
+      <c r="C11" s="104"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="105"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H15" s="77">
@@ -4707,7 +5032,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист7">
     <tabColor rgb="FF92D050"/>
@@ -4937,7 +5262,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист8">
     <tabColor rgb="FF00B050"/>
@@ -5199,7 +5524,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист9">
     <tabColor rgb="FF00B050"/>
@@ -5382,7 +5707,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист10">
     <tabColor rgb="FF92D050"/>
@@ -5545,7 +5870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист11"/>
   <dimension ref="A1:F2"/>
@@ -5606,7 +5931,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист12">
     <tabColor rgb="FF92D050"/>
@@ -5769,7 +6094,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист13"/>
   <dimension ref="A1:F2"/>
@@ -5830,7 +6155,131 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="96" t="s">
+        <v>814</v>
+      </c>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
+        <v>815</v>
+      </c>
+      <c r="B2" s="97" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="83" t="s">
+        <v>758</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="67" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="82">
+        <v>1</v>
+      </c>
+      <c r="B3" s="100" t="s">
+        <v>439</v>
+      </c>
+      <c r="C3" s="101"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="84" t="s">
+        <v>926</v>
+      </c>
+      <c r="F3" s="82" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="70">
+        <v>1959.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="103"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="103"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="82" t="s">
+        <v>831</v>
+      </c>
+      <c r="B5" s="82" t="s">
+        <v>821</v>
+      </c>
+      <c r="C5" s="104"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="82">
+        <v>-1</v>
+      </c>
+      <c r="B6" s="70">
+        <v>1959.9</v>
+      </c>
+      <c r="C6" s="104"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="105"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="85" t="s">
+        <v>828</v>
+      </c>
+      <c r="B7" s="70">
+        <f>SUM(B6:B6)</f>
+        <v>1959.9</v>
+      </c>
+      <c r="C7" s="104"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="C5:G7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист14">
     <tabColor rgb="FF92D050"/>
@@ -5993,7 +6442,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист15"/>
   <dimension ref="A1:F2"/>
@@ -6054,185 +6503,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Лист17"/>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" customWidth="1"/>
-    <col min="3" max="3" width="6.33203125" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="92" t="s">
-        <v>814</v>
-      </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-    </row>
-    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="65" t="s">
-        <v>815</v>
-      </c>
-      <c r="B2" s="93" t="s">
-        <v>816</v>
-      </c>
-      <c r="C2" s="94"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="79" t="s">
-        <v>758</v>
-      </c>
-      <c r="F2" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="67" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="78">
-        <v>1</v>
-      </c>
-      <c r="B3" s="96" t="s">
-        <v>439</v>
-      </c>
-      <c r="C3" s="97"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="80" t="s">
-        <v>829</v>
-      </c>
-      <c r="F3" s="78" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="70">
-        <f>B11</f>
-        <v>4716.6000000000004</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="99"/>
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="78" t="s">
-        <v>831</v>
-      </c>
-      <c r="B5" s="78" t="s">
-        <v>821</v>
-      </c>
-      <c r="C5" s="100"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
-    </row>
-    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="78">
-        <v>1</v>
-      </c>
-      <c r="B6" s="70">
-        <v>905.8</v>
-      </c>
-      <c r="C6" s="100"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="101"/>
-    </row>
-    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="78">
-        <v>2</v>
-      </c>
-      <c r="B7" s="70">
-        <v>911.4</v>
-      </c>
-      <c r="C7" s="100"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="101"/>
-    </row>
-    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="78">
-        <v>3</v>
-      </c>
-      <c r="B8" s="70">
-        <v>905.40000000000009</v>
-      </c>
-      <c r="C8" s="100"/>
-      <c r="D8" s="101"/>
-      <c r="E8" s="101"/>
-      <c r="F8" s="101"/>
-      <c r="G8" s="101"/>
-    </row>
-    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="78">
-        <v>4</v>
-      </c>
-      <c r="B9" s="70">
-        <v>1005.4000000000001</v>
-      </c>
-      <c r="C9" s="100"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
-    </row>
-    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="78">
-        <v>5</v>
-      </c>
-      <c r="B10" s="70">
-        <v>988.60000000000014</v>
-      </c>
-      <c r="C10" s="100"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
-      <c r="F10" s="101"/>
-      <c r="G10" s="101"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="81" t="s">
-        <v>828</v>
-      </c>
-      <c r="B11" s="70">
-        <f>SUM(B6:B10)</f>
-        <v>4716.6000000000004</v>
-      </c>
-      <c r="C11" s="100"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="101"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="C5:G11"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист16">
     <tabColor rgb="FF00B050"/>
@@ -6437,6 +6708,184 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист17"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="96" t="s">
+        <v>814</v>
+      </c>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
+        <v>815</v>
+      </c>
+      <c r="B2" s="97" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="79" t="s">
+        <v>758</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="67" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="78">
+        <v>1</v>
+      </c>
+      <c r="B3" s="100" t="s">
+        <v>439</v>
+      </c>
+      <c r="C3" s="101"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="80" t="s">
+        <v>829</v>
+      </c>
+      <c r="F3" s="78" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="70">
+        <f>B11</f>
+        <v>4716.6000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="103"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="103"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="78" t="s">
+        <v>831</v>
+      </c>
+      <c r="B5" s="78" t="s">
+        <v>821</v>
+      </c>
+      <c r="C5" s="104"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="78">
+        <v>1</v>
+      </c>
+      <c r="B6" s="70">
+        <v>905.8</v>
+      </c>
+      <c r="C6" s="104"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="105"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="78">
+        <v>2</v>
+      </c>
+      <c r="B7" s="70">
+        <v>911.4</v>
+      </c>
+      <c r="C7" s="104"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="78">
+        <v>3</v>
+      </c>
+      <c r="B8" s="70">
+        <v>905.40000000000009</v>
+      </c>
+      <c r="C8" s="104"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="78">
+        <v>4</v>
+      </c>
+      <c r="B9" s="70">
+        <v>1005.4000000000001</v>
+      </c>
+      <c r="C9" s="104"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="78">
+        <v>5</v>
+      </c>
+      <c r="B10" s="70">
+        <v>988.60000000000014</v>
+      </c>
+      <c r="C10" s="104"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="81" t="s">
+        <v>828</v>
+      </c>
+      <c r="B11" s="70">
+        <f>SUM(B6:B10)</f>
+        <v>4716.6000000000004</v>
+      </c>
+      <c r="C11" s="104"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="105"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="C5:G11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист1">
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
@@ -7771,7 +8220,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист2">
     <tabColor rgb="FF00B050"/>
@@ -7899,7 +8348,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист3"/>
   <dimension ref="A1:N22"/>
@@ -7915,25 +8364,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="96" t="s">
         <v>814</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="65" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="102" t="s">
+      <c r="B2" s="106" t="s">
         <v>816</v>
       </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="104"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="108"/>
       <c r="E2" s="66" t="s">
         <v>758</v>
       </c>
@@ -7948,11 +8397,11 @@
       <c r="A3" s="68">
         <v>1</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="109" t="s">
         <v>516</v>
       </c>
-      <c r="C3" s="106"/>
-      <c r="D3" s="107"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="111"/>
       <c r="E3" s="69" t="s">
         <v>830</v>
       </c>
@@ -7965,24 +8414,24 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="99"/>
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="103"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="108" t="s">
+      <c r="A5" s="112" t="s">
         <v>818</v>
       </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
+      <c r="B5" s="112"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="68" t="s">
@@ -7997,9 +8446,9 @@
       <c r="D6" s="68" t="s">
         <v>822</v>
       </c>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="101"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="105"/>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="68">
@@ -8015,9 +8464,9 @@
       <c r="D7" s="71">
         <v>228</v>
       </c>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="101"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="68">
@@ -8033,9 +8482,9 @@
       <c r="D8" s="71">
         <v>247.1</v>
       </c>
-      <c r="E8" s="101"/>
-      <c r="F8" s="101"/>
-      <c r="G8" s="101"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
     </row>
     <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="68">
@@ -8051,9 +8500,9 @@
       <c r="D9" s="71">
         <v>243.6</v>
       </c>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="68">
@@ -8069,9 +8518,9 @@
       <c r="D10" s="71">
         <v>243.6</v>
       </c>
-      <c r="E10" s="101"/>
-      <c r="F10" s="101"/>
-      <c r="G10" s="101"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="68">
@@ -8087,15 +8536,15 @@
       <c r="D11" s="71">
         <v>117.4</v>
       </c>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="101"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="105"/>
     </row>
     <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="109" t="s">
+      <c r="A12" s="113" t="s">
         <v>828</v>
       </c>
-      <c r="B12" s="110"/>
+      <c r="B12" s="114"/>
       <c r="C12" s="73">
         <f>SUM(C7:C11)</f>
         <v>4102.8599999999997</v>
@@ -8103,9 +8552,9 @@
       <c r="D12" s="73">
         <v>1200</v>
       </c>
-      <c r="E12" s="101"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="101"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
     </row>
     <row r="17" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I17" t="s">
@@ -8232,7 +8681,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист4"/>
   <dimension ref="A1:R528"/>
@@ -8292,61 +8741,61 @@
       <c r="O1" s="19"/>
     </row>
     <row r="2" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="115" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
-      <c r="O2" s="121"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="115"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="115"/>
+      <c r="M2" s="115"/>
+      <c r="N2" s="115"/>
+      <c r="O2" s="115"/>
     </row>
     <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="122" t="s">
+      <c r="A3" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="122"/>
-      <c r="K3" s="122"/>
-      <c r="L3" s="122"/>
-      <c r="M3" s="122"/>
-      <c r="N3" s="122"/>
-      <c r="O3" s="122"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="116"/>
+      <c r="J3" s="116"/>
+      <c r="K3" s="116"/>
+      <c r="L3" s="116"/>
+      <c r="M3" s="116"/>
+      <c r="N3" s="116"/>
+      <c r="O3" s="116"/>
     </row>
     <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="121" t="s">
+      <c r="A4" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="121"/>
-      <c r="C4" s="121"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121"/>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="115"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="115"/>
+      <c r="L4" s="115"/>
+      <c r="M4" s="115"/>
+      <c r="N4" s="115"/>
+      <c r="O4" s="115"/>
     </row>
     <row r="5" spans="1:18" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
@@ -8399,17 +8848,17 @@
       <c r="R5" s="13"/>
     </row>
     <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="119" t="s">
+      <c r="A6" s="117" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="120"/>
-      <c r="C6" s="120"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="120"/>
-      <c r="G6" s="120"/>
-      <c r="H6" s="120"/>
-      <c r="I6" s="120"/>
+      <c r="B6" s="118"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="118"/>
+      <c r="H6" s="118"/>
+      <c r="I6" s="118"/>
       <c r="J6" s="21"/>
       <c r="K6" s="21"/>
       <c r="L6" s="21"/>
@@ -8425,15 +8874,15 @@
       <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="115" t="s">
+      <c r="C7" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="120"/>
+      <c r="F7" s="120"/>
+      <c r="G7" s="120"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="120"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
@@ -8449,15 +8898,15 @@
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="115" t="s">
+      <c r="C8" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="116"/>
-      <c r="E8" s="116"/>
-      <c r="F8" s="116"/>
-      <c r="G8" s="116"/>
-      <c r="H8" s="116"/>
-      <c r="I8" s="116"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="120"/>
+      <c r="F8" s="120"/>
+      <c r="G8" s="120"/>
+      <c r="H8" s="120"/>
+      <c r="I8" s="120"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
@@ -8473,15 +8922,15 @@
       <c r="B9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="115" t="s">
+      <c r="C9" s="119" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="116"/>
-      <c r="E9" s="116"/>
-      <c r="F9" s="116"/>
-      <c r="G9" s="116"/>
-      <c r="H9" s="116"/>
-      <c r="I9" s="116"/>
+      <c r="D9" s="120"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+      <c r="G9" s="120"/>
+      <c r="H9" s="120"/>
+      <c r="I9" s="120"/>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
@@ -8497,15 +8946,15 @@
       <c r="B10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="115" t="s">
+      <c r="C10" s="119" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="116"/>
-      <c r="E10" s="116"/>
-      <c r="F10" s="116"/>
-      <c r="G10" s="116"/>
-      <c r="H10" s="116"/>
-      <c r="I10" s="116"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="120"/>
+      <c r="H10" s="120"/>
+      <c r="I10" s="120"/>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
@@ -8521,15 +8970,15 @@
       <c r="B11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="115" t="s">
+      <c r="C11" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="116"/>
-      <c r="E11" s="116"/>
-      <c r="F11" s="116"/>
-      <c r="G11" s="116"/>
-      <c r="H11" s="116"/>
-      <c r="I11" s="116"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="120"/>
+      <c r="F11" s="120"/>
+      <c r="G11" s="120"/>
+      <c r="H11" s="120"/>
+      <c r="I11" s="120"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
@@ -8545,15 +8994,15 @@
       <c r="B12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="115" t="s">
+      <c r="C12" s="119" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="116"/>
-      <c r="E12" s="116"/>
-      <c r="F12" s="116"/>
-      <c r="G12" s="116"/>
-      <c r="H12" s="116"/>
-      <c r="I12" s="116"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="120"/>
+      <c r="F12" s="120"/>
+      <c r="G12" s="120"/>
+      <c r="H12" s="120"/>
+      <c r="I12" s="120"/>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
@@ -11591,15 +12040,15 @@
       <c r="B108" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C108" s="115" t="s">
+      <c r="C108" s="119" t="s">
         <v>166</v>
       </c>
-      <c r="D108" s="116"/>
-      <c r="E108" s="116"/>
-      <c r="F108" s="116"/>
-      <c r="G108" s="116"/>
-      <c r="H108" s="116"/>
-      <c r="I108" s="116"/>
+      <c r="D108" s="120"/>
+      <c r="E108" s="120"/>
+      <c r="F108" s="120"/>
+      <c r="G108" s="120"/>
+      <c r="H108" s="120"/>
+      <c r="I108" s="120"/>
       <c r="J108" s="9"/>
       <c r="K108" s="9"/>
       <c r="L108" s="9"/>
@@ -11615,15 +12064,15 @@
       <c r="B109" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C109" s="115" t="s">
+      <c r="C109" s="119" t="s">
         <v>169</v>
       </c>
-      <c r="D109" s="116"/>
-      <c r="E109" s="116"/>
-      <c r="F109" s="116"/>
-      <c r="G109" s="116"/>
-      <c r="H109" s="116"/>
-      <c r="I109" s="116"/>
+      <c r="D109" s="120"/>
+      <c r="E109" s="120"/>
+      <c r="F109" s="120"/>
+      <c r="G109" s="120"/>
+      <c r="H109" s="120"/>
+      <c r="I109" s="120"/>
       <c r="J109" s="9"/>
       <c r="K109" s="9"/>
       <c r="L109" s="9"/>
@@ -11639,15 +12088,15 @@
       <c r="B110" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C110" s="115" t="s">
+      <c r="C110" s="119" t="s">
         <v>172</v>
       </c>
-      <c r="D110" s="116"/>
-      <c r="E110" s="116"/>
-      <c r="F110" s="116"/>
-      <c r="G110" s="116"/>
-      <c r="H110" s="116"/>
-      <c r="I110" s="116"/>
+      <c r="D110" s="120"/>
+      <c r="E110" s="120"/>
+      <c r="F110" s="120"/>
+      <c r="G110" s="120"/>
+      <c r="H110" s="120"/>
+      <c r="I110" s="120"/>
       <c r="J110" s="9"/>
       <c r="K110" s="9"/>
       <c r="L110" s="9"/>
@@ -11663,15 +12112,15 @@
       <c r="B111" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C111" s="115" t="s">
+      <c r="C111" s="119" t="s">
         <v>175</v>
       </c>
-      <c r="D111" s="116"/>
-      <c r="E111" s="116"/>
-      <c r="F111" s="116"/>
-      <c r="G111" s="116"/>
-      <c r="H111" s="116"/>
-      <c r="I111" s="116"/>
+      <c r="D111" s="120"/>
+      <c r="E111" s="120"/>
+      <c r="F111" s="120"/>
+      <c r="G111" s="120"/>
+      <c r="H111" s="120"/>
+      <c r="I111" s="120"/>
       <c r="J111" s="9"/>
       <c r="K111" s="9"/>
       <c r="L111" s="9"/>
@@ -11687,15 +12136,15 @@
       <c r="B112" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C112" s="115" t="s">
+      <c r="C112" s="119" t="s">
         <v>178</v>
       </c>
-      <c r="D112" s="116"/>
-      <c r="E112" s="116"/>
-      <c r="F112" s="116"/>
-      <c r="G112" s="116"/>
-      <c r="H112" s="116"/>
-      <c r="I112" s="116"/>
+      <c r="D112" s="120"/>
+      <c r="E112" s="120"/>
+      <c r="F112" s="120"/>
+      <c r="G112" s="120"/>
+      <c r="H112" s="120"/>
+      <c r="I112" s="120"/>
       <c r="J112" s="9"/>
       <c r="K112" s="9"/>
       <c r="L112" s="9"/>
@@ -12422,15 +12871,15 @@
       <c r="B135" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C135" s="115" t="s">
+      <c r="C135" s="119" t="s">
         <v>219</v>
       </c>
-      <c r="D135" s="116"/>
-      <c r="E135" s="116"/>
-      <c r="F135" s="116"/>
-      <c r="G135" s="116"/>
-      <c r="H135" s="116"/>
-      <c r="I135" s="116"/>
+      <c r="D135" s="120"/>
+      <c r="E135" s="120"/>
+      <c r="F135" s="120"/>
+      <c r="G135" s="120"/>
+      <c r="H135" s="120"/>
+      <c r="I135" s="120"/>
       <c r="J135" s="9"/>
       <c r="K135" s="9"/>
       <c r="L135" s="9"/>
@@ -13957,15 +14406,15 @@
       <c r="B180" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C180" s="115" t="s">
+      <c r="C180" s="119" t="s">
         <v>285</v>
       </c>
-      <c r="D180" s="116"/>
-      <c r="E180" s="116"/>
-      <c r="F180" s="116"/>
-      <c r="G180" s="116"/>
-      <c r="H180" s="116"/>
-      <c r="I180" s="116"/>
+      <c r="D180" s="120"/>
+      <c r="E180" s="120"/>
+      <c r="F180" s="120"/>
+      <c r="G180" s="120"/>
+      <c r="H180" s="120"/>
+      <c r="I180" s="120"/>
       <c r="J180" s="9"/>
       <c r="K180" s="9"/>
       <c r="L180" s="9"/>
@@ -17318,15 +17767,15 @@
       <c r="B285" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C285" s="115" t="s">
+      <c r="C285" s="119" t="s">
         <v>433</v>
       </c>
-      <c r="D285" s="116"/>
-      <c r="E285" s="116"/>
-      <c r="F285" s="116"/>
-      <c r="G285" s="116"/>
-      <c r="H285" s="116"/>
-      <c r="I285" s="116"/>
+      <c r="D285" s="120"/>
+      <c r="E285" s="120"/>
+      <c r="F285" s="120"/>
+      <c r="G285" s="120"/>
+      <c r="H285" s="120"/>
+      <c r="I285" s="120"/>
       <c r="J285" s="9"/>
       <c r="K285" s="9"/>
       <c r="L285" s="9"/>
@@ -17342,15 +17791,15 @@
       <c r="B286" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C286" s="115" t="s">
+      <c r="C286" s="119" t="s">
         <v>436</v>
       </c>
-      <c r="D286" s="116"/>
-      <c r="E286" s="116"/>
-      <c r="F286" s="116"/>
-      <c r="G286" s="116"/>
-      <c r="H286" s="116"/>
-      <c r="I286" s="116"/>
+      <c r="D286" s="120"/>
+      <c r="E286" s="120"/>
+      <c r="F286" s="120"/>
+      <c r="G286" s="120"/>
+      <c r="H286" s="120"/>
+      <c r="I286" s="120"/>
       <c r="J286" s="9"/>
       <c r="K286" s="9"/>
       <c r="L286" s="9"/>
@@ -17687,15 +18136,15 @@
       <c r="B297" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="C297" s="115" t="s">
+      <c r="C297" s="119" t="s">
         <v>455</v>
       </c>
-      <c r="D297" s="116"/>
-      <c r="E297" s="116"/>
-      <c r="F297" s="116"/>
-      <c r="G297" s="116"/>
-      <c r="H297" s="116"/>
-      <c r="I297" s="116"/>
+      <c r="D297" s="120"/>
+      <c r="E297" s="120"/>
+      <c r="F297" s="120"/>
+      <c r="G297" s="120"/>
+      <c r="H297" s="120"/>
+      <c r="I297" s="120"/>
       <c r="J297" s="9"/>
       <c r="K297" s="9"/>
       <c r="L297" s="9"/>
@@ -18565,15 +19014,15 @@
       <c r="B324" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="C324" s="115" t="s">
+      <c r="C324" s="119" t="s">
         <v>498</v>
       </c>
-      <c r="D324" s="116"/>
-      <c r="E324" s="116"/>
-      <c r="F324" s="116"/>
-      <c r="G324" s="116"/>
-      <c r="H324" s="116"/>
-      <c r="I324" s="116"/>
+      <c r="D324" s="120"/>
+      <c r="E324" s="120"/>
+      <c r="F324" s="120"/>
+      <c r="G324" s="120"/>
+      <c r="H324" s="120"/>
+      <c r="I324" s="120"/>
       <c r="J324" s="9"/>
       <c r="K324" s="9"/>
       <c r="L324" s="9"/>
@@ -18589,15 +19038,15 @@
       <c r="B325" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="C325" s="115" t="s">
+      <c r="C325" s="119" t="s">
         <v>501</v>
       </c>
-      <c r="D325" s="116"/>
-      <c r="E325" s="116"/>
-      <c r="F325" s="116"/>
-      <c r="G325" s="116"/>
-      <c r="H325" s="116"/>
-      <c r="I325" s="116"/>
+      <c r="D325" s="120"/>
+      <c r="E325" s="120"/>
+      <c r="F325" s="120"/>
+      <c r="G325" s="120"/>
+      <c r="H325" s="120"/>
+      <c r="I325" s="120"/>
       <c r="J325" s="9"/>
       <c r="K325" s="9"/>
       <c r="L325" s="9"/>
@@ -19127,15 +19576,15 @@
       <c r="B342" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="C342" s="115" t="s">
+      <c r="C342" s="119" t="s">
         <v>525</v>
       </c>
-      <c r="D342" s="116"/>
-      <c r="E342" s="116"/>
-      <c r="F342" s="116"/>
-      <c r="G342" s="116"/>
-      <c r="H342" s="116"/>
-      <c r="I342" s="116"/>
+      <c r="D342" s="120"/>
+      <c r="E342" s="120"/>
+      <c r="F342" s="120"/>
+      <c r="G342" s="120"/>
+      <c r="H342" s="120"/>
+      <c r="I342" s="120"/>
       <c r="J342" s="9"/>
       <c r="K342" s="9"/>
       <c r="L342" s="9"/>
@@ -19947,15 +20396,15 @@
       <c r="B367" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="C367" s="115" t="s">
+      <c r="C367" s="119" t="s">
         <v>559</v>
       </c>
-      <c r="D367" s="116"/>
-      <c r="E367" s="116"/>
-      <c r="F367" s="116"/>
-      <c r="G367" s="116"/>
-      <c r="H367" s="116"/>
-      <c r="I367" s="116"/>
+      <c r="D367" s="120"/>
+      <c r="E367" s="120"/>
+      <c r="F367" s="120"/>
+      <c r="G367" s="120"/>
+      <c r="H367" s="120"/>
+      <c r="I367" s="120"/>
       <c r="J367" s="9"/>
       <c r="K367" s="9"/>
       <c r="L367" s="9"/>
@@ -22459,15 +22908,15 @@
       <c r="B447" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="C447" s="115" t="s">
+      <c r="C447" s="119" t="s">
         <v>664</v>
       </c>
-      <c r="D447" s="116"/>
-      <c r="E447" s="116"/>
-      <c r="F447" s="116"/>
-      <c r="G447" s="116"/>
-      <c r="H447" s="116"/>
-      <c r="I447" s="116"/>
+      <c r="D447" s="120"/>
+      <c r="E447" s="120"/>
+      <c r="F447" s="120"/>
+      <c r="G447" s="120"/>
+      <c r="H447" s="120"/>
+      <c r="I447" s="120"/>
       <c r="J447" s="9"/>
       <c r="K447" s="9"/>
       <c r="L447" s="9"/>
@@ -22555,17 +23004,17 @@
       <c r="P449" s="9"/>
     </row>
     <row r="450" spans="1:18" ht="64.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A450" s="119" t="s">
+      <c r="A450" s="117" t="s">
         <v>671</v>
       </c>
-      <c r="B450" s="120"/>
-      <c r="C450" s="120"/>
-      <c r="D450" s="120"/>
-      <c r="E450" s="120"/>
-      <c r="F450" s="120"/>
-      <c r="G450" s="120"/>
-      <c r="H450" s="120"/>
-      <c r="I450" s="120"/>
+      <c r="B450" s="118"/>
+      <c r="C450" s="118"/>
+      <c r="D450" s="118"/>
+      <c r="E450" s="118"/>
+      <c r="F450" s="118"/>
+      <c r="G450" s="118"/>
+      <c r="H450" s="118"/>
+      <c r="I450" s="118"/>
       <c r="J450" s="26"/>
       <c r="K450" s="26"/>
       <c r="L450" s="26"/>
@@ -22581,15 +23030,15 @@
       <c r="B451" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C451" s="115" t="s">
+      <c r="C451" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="D451" s="116"/>
-      <c r="E451" s="116"/>
-      <c r="F451" s="116"/>
-      <c r="G451" s="116"/>
-      <c r="H451" s="116"/>
-      <c r="I451" s="116"/>
+      <c r="D451" s="120"/>
+      <c r="E451" s="120"/>
+      <c r="F451" s="120"/>
+      <c r="G451" s="120"/>
+      <c r="H451" s="120"/>
+      <c r="I451" s="120"/>
       <c r="J451" s="9"/>
       <c r="K451" s="9"/>
       <c r="L451" s="9"/>
@@ -22605,15 +23054,15 @@
       <c r="B452" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C452" s="115" t="s">
+      <c r="C452" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="D452" s="116"/>
-      <c r="E452" s="116"/>
-      <c r="F452" s="116"/>
-      <c r="G452" s="116"/>
-      <c r="H452" s="116"/>
-      <c r="I452" s="116"/>
+      <c r="D452" s="120"/>
+      <c r="E452" s="120"/>
+      <c r="F452" s="120"/>
+      <c r="G452" s="120"/>
+      <c r="H452" s="120"/>
+      <c r="I452" s="120"/>
       <c r="J452" s="9"/>
       <c r="K452" s="9"/>
       <c r="L452" s="9"/>
@@ -22629,15 +23078,15 @@
       <c r="B453" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C453" s="115" t="s">
+      <c r="C453" s="119" t="s">
         <v>31</v>
       </c>
-      <c r="D453" s="116"/>
-      <c r="E453" s="116"/>
-      <c r="F453" s="116"/>
-      <c r="G453" s="116"/>
-      <c r="H453" s="116"/>
-      <c r="I453" s="116"/>
+      <c r="D453" s="120"/>
+      <c r="E453" s="120"/>
+      <c r="F453" s="120"/>
+      <c r="G453" s="120"/>
+      <c r="H453" s="120"/>
+      <c r="I453" s="120"/>
       <c r="J453" s="9"/>
       <c r="K453" s="9"/>
       <c r="L453" s="9"/>
@@ -22653,15 +23102,15 @@
       <c r="B454" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C454" s="115" t="s">
+      <c r="C454" s="119" t="s">
         <v>34</v>
       </c>
-      <c r="D454" s="116"/>
-      <c r="E454" s="116"/>
-      <c r="F454" s="116"/>
-      <c r="G454" s="116"/>
-      <c r="H454" s="116"/>
-      <c r="I454" s="116"/>
+      <c r="D454" s="120"/>
+      <c r="E454" s="120"/>
+      <c r="F454" s="120"/>
+      <c r="G454" s="120"/>
+      <c r="H454" s="120"/>
+      <c r="I454" s="120"/>
       <c r="J454" s="9"/>
       <c r="K454" s="9"/>
       <c r="L454" s="9"/>
@@ -22677,15 +23126,15 @@
       <c r="B455" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C455" s="115" t="s">
+      <c r="C455" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="D455" s="116"/>
-      <c r="E455" s="116"/>
-      <c r="F455" s="116"/>
-      <c r="G455" s="116"/>
-      <c r="H455" s="116"/>
-      <c r="I455" s="116"/>
+      <c r="D455" s="120"/>
+      <c r="E455" s="120"/>
+      <c r="F455" s="120"/>
+      <c r="G455" s="120"/>
+      <c r="H455" s="120"/>
+      <c r="I455" s="120"/>
       <c r="J455" s="9"/>
       <c r="K455" s="9"/>
       <c r="L455" s="9"/>
@@ -22701,15 +23150,15 @@
       <c r="B456" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="C456" s="117" t="s">
+      <c r="C456" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="D456" s="118"/>
-      <c r="E456" s="118"/>
-      <c r="F456" s="118"/>
-      <c r="G456" s="118"/>
-      <c r="H456" s="118"/>
-      <c r="I456" s="118"/>
+      <c r="D456" s="126"/>
+      <c r="E456" s="126"/>
+      <c r="F456" s="126"/>
+      <c r="G456" s="126"/>
+      <c r="H456" s="126"/>
+      <c r="I456" s="126"/>
       <c r="J456" s="27"/>
       <c r="K456" s="27"/>
       <c r="L456" s="27"/>
@@ -24272,15 +24721,15 @@
       <c r="B505" s="30" t="s">
         <v>432</v>
       </c>
-      <c r="C505" s="113" t="s">
+      <c r="C505" s="123" t="s">
         <v>433</v>
       </c>
-      <c r="D505" s="114"/>
-      <c r="E505" s="114"/>
-      <c r="F505" s="114"/>
-      <c r="G505" s="114"/>
-      <c r="H505" s="114"/>
-      <c r="I505" s="114"/>
+      <c r="D505" s="124"/>
+      <c r="E505" s="124"/>
+      <c r="F505" s="124"/>
+      <c r="G505" s="124"/>
+      <c r="H505" s="124"/>
+      <c r="I505" s="124"/>
       <c r="J505" s="9"/>
       <c r="K505" s="29"/>
       <c r="L505" s="9"/>
@@ -24296,15 +24745,15 @@
       <c r="B506" s="30" t="s">
         <v>435</v>
       </c>
-      <c r="C506" s="113" t="s">
+      <c r="C506" s="123" t="s">
         <v>436</v>
       </c>
-      <c r="D506" s="114"/>
-      <c r="E506" s="114"/>
-      <c r="F506" s="114"/>
-      <c r="G506" s="114"/>
-      <c r="H506" s="114"/>
-      <c r="I506" s="114"/>
+      <c r="D506" s="124"/>
+      <c r="E506" s="124"/>
+      <c r="F506" s="124"/>
+      <c r="G506" s="124"/>
+      <c r="H506" s="124"/>
+      <c r="I506" s="124"/>
       <c r="J506" s="9"/>
       <c r="K506" s="29"/>
       <c r="L506" s="9"/>
@@ -24466,15 +24915,15 @@
       <c r="B512" s="30" t="s">
         <v>454</v>
       </c>
-      <c r="C512" s="113" t="s">
+      <c r="C512" s="123" t="s">
         <v>455</v>
       </c>
-      <c r="D512" s="114"/>
-      <c r="E512" s="114"/>
-      <c r="F512" s="114"/>
-      <c r="G512" s="114"/>
-      <c r="H512" s="114"/>
-      <c r="I512" s="114"/>
+      <c r="D512" s="124"/>
+      <c r="E512" s="124"/>
+      <c r="F512" s="124"/>
+      <c r="G512" s="124"/>
+      <c r="H512" s="124"/>
+      <c r="I512" s="124"/>
       <c r="J512" s="9"/>
       <c r="K512" s="29"/>
       <c r="L512" s="9"/>
@@ -24601,7 +25050,7 @@
       <c r="O516" s="9"/>
       <c r="P516" s="9"/>
     </row>
-    <row r="517" spans="1:16" ht="90" hidden="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" s="1" t="s">
         <v>740</v>
       </c>
@@ -24663,7 +25112,7 @@
       <c r="O518" s="8"/>
       <c r="P518" s="9"/>
     </row>
-    <row r="519" spans="1:16" ht="90" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" s="1" t="s">
         <v>742</v>
       </c>
@@ -24911,22 +25360,35 @@
       <c r="E528" s="54"/>
       <c r="F528" s="54"/>
       <c r="G528" s="54"/>
-      <c r="H528" s="111"/>
-      <c r="I528" s="112"/>
-      <c r="J528" s="112"/>
-      <c r="K528" s="112"/>
-      <c r="L528" s="112"/>
-      <c r="M528" s="112"/>
-      <c r="N528" s="112"/>
-      <c r="O528" s="112"/>
+      <c r="H528" s="121"/>
+      <c r="I528" s="122"/>
+      <c r="J528" s="122"/>
+      <c r="K528" s="122"/>
+      <c r="L528" s="122"/>
+      <c r="M528" s="122"/>
+      <c r="N528" s="122"/>
+      <c r="O528" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A4:O4"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="H528:O528"/>
+    <mergeCell ref="C505:I505"/>
+    <mergeCell ref="C506:I506"/>
+    <mergeCell ref="C512:I512"/>
+    <mergeCell ref="C455:I455"/>
+    <mergeCell ref="C456:I456"/>
+    <mergeCell ref="C454:I454"/>
+    <mergeCell ref="C286:I286"/>
+    <mergeCell ref="C297:I297"/>
+    <mergeCell ref="C324:I324"/>
+    <mergeCell ref="C325:I325"/>
+    <mergeCell ref="C342:I342"/>
+    <mergeCell ref="C367:I367"/>
+    <mergeCell ref="C447:I447"/>
+    <mergeCell ref="A450:I450"/>
+    <mergeCell ref="C451:I451"/>
+    <mergeCell ref="C452:I452"/>
+    <mergeCell ref="C453:I453"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="C285:I285"/>
     <mergeCell ref="C9:I9"/>
@@ -24940,31 +25402,18 @@
     <mergeCell ref="C112:I112"/>
     <mergeCell ref="C135:I135"/>
     <mergeCell ref="C180:I180"/>
-    <mergeCell ref="C454:I454"/>
-    <mergeCell ref="C286:I286"/>
-    <mergeCell ref="C297:I297"/>
-    <mergeCell ref="C324:I324"/>
-    <mergeCell ref="C325:I325"/>
-    <mergeCell ref="C342:I342"/>
-    <mergeCell ref="C367:I367"/>
-    <mergeCell ref="C447:I447"/>
-    <mergeCell ref="A450:I450"/>
-    <mergeCell ref="C451:I451"/>
-    <mergeCell ref="C452:I452"/>
-    <mergeCell ref="C453:I453"/>
-    <mergeCell ref="H528:O528"/>
-    <mergeCell ref="C505:I505"/>
-    <mergeCell ref="C506:I506"/>
-    <mergeCell ref="C512:I512"/>
-    <mergeCell ref="C455:I455"/>
-    <mergeCell ref="C456:I456"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="C7:I7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист5"/>
   <dimension ref="A1:F8"/>
@@ -24980,23 +25429,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="96" t="s">
         <v>814</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
     </row>
     <row r="2" spans="1:6" s="77" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="76" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="123" t="s">
+      <c r="B2" s="127" t="s">
         <v>816</v>
       </c>
-      <c r="C2" s="124"/>
+      <c r="C2" s="128"/>
       <c r="D2" s="76" t="s">
         <v>758</v>
       </c>
@@ -25011,10 +25460,10 @@
       <c r="A3" s="68">
         <v>1</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="109" t="s">
         <v>832</v>
       </c>
-      <c r="C3" s="107"/>
+      <c r="C3" s="111"/>
       <c r="D3" s="75" t="s">
         <v>834</v>
       </c>
@@ -25027,12 +25476,12 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="99"/>
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="103"/>
     </row>
     <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="68" t="s">
@@ -25041,10 +25490,10 @@
       <c r="B5" s="68" t="s">
         <v>821</v>
       </c>
-      <c r="C5" s="100"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
     </row>
     <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="68">
@@ -25053,10 +25502,10 @@
       <c r="B6" s="70">
         <v>806</v>
       </c>
-      <c r="C6" s="100"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
     </row>
     <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="68">
@@ -25065,10 +25514,10 @@
       <c r="B7" s="70">
         <v>788.8</v>
       </c>
-      <c r="C7" s="100"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
     </row>
     <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="74" t="s">
@@ -25078,10 +25527,10 @@
         <f>SUM(B6:B7)</f>
         <v>1594.8</v>
       </c>
-      <c r="C8" s="100"/>
-      <c r="D8" s="101"/>
-      <c r="E8" s="101"/>
-      <c r="F8" s="101"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -25095,12 +25544,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
@@ -25128,7 +25577,7 @@
         <v>18</v>
       </c>
       <c r="F1" s="60" t="s">
-        <v>813</v>
+        <v>766</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.3">
@@ -25148,7 +25597,7 @@
         <v>46</v>
       </c>
       <c r="F2" s="59">
-        <v>671</v>
+        <v>382.23900000000003</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.3">
@@ -25156,19 +25605,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>807</v>
+        <v>760</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="8">
-        <v>93.1</v>
+      <c r="F3" s="59">
+        <v>12.4245</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.3">
@@ -25179,16 +25628,16 @@
         <v>98</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>46</v>
       </c>
       <c r="F4" s="8">
-        <v>24.4</v>
+        <v>30.492000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.3">
@@ -25199,16 +25648,16 @@
         <v>98</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>811</v>
+        <v>756</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>46</v>
       </c>
       <c r="F5" s="8">
-        <v>262.60000000000002</v>
+        <v>4.0179999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.3">
@@ -25219,132 +25668,79 @@
         <v>98</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>755</v>
+        <v>811</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>46</v>
       </c>
       <c r="F6" s="8">
-        <v>9.15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="54" x14ac:dyDescent="0.3">
+        <v>150.52799999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="42">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>46</v>
       </c>
       <c r="F7" s="8">
-        <v>10.55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+        <v>15.617000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A8" s="42">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>46</v>
       </c>
       <c r="F8" s="8">
-        <v>9.0500000000000007</v>
+        <v>18.769500000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="42">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="8">
+        <v>5.3835000000000006</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" customWidth="1"/>
-    <col min="3" max="3" width="6.33203125" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="92" t="s">
-        <v>814</v>
-      </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-    </row>
-    <row r="2" spans="1:7" s="77" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="89" t="s">
-        <v>815</v>
-      </c>
-      <c r="B2" s="123" t="s">
-        <v>816</v>
-      </c>
-      <c r="C2" s="125"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="91" t="s">
-        <v>758</v>
-      </c>
-      <c r="F2" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="67" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="89">
-        <v>1</v>
-      </c>
-      <c r="B3" s="96" t="s">
-        <v>439</v>
-      </c>
-      <c r="C3" s="97"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="90" t="s">
-        <v>927</v>
-      </c>
-      <c r="F3" s="89" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="70">
-        <v>2924.7</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/hospital/стены/hospital-walls.xlsx
+++ b/hospital/стены/hospital-walls.xlsx
@@ -4,38 +4,44 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" codeName="ЭтаКнига" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="898" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="898" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="5.1Шлф" sheetId="24" r:id="rId1"/>
-    <sheet name="2.6шт" sheetId="20" r:id="rId2"/>
-    <sheet name="2.5шт" sheetId="19" r:id="rId3"/>
-    <sheet name="Общ" sheetId="18" r:id="rId4"/>
-    <sheet name="2.4ГВЛ" sheetId="17" r:id="rId5"/>
+    <sheet name="Общ2" sheetId="27" r:id="rId1"/>
+    <sheet name="Общ" sheetId="18" r:id="rId2"/>
+    <sheet name="5.3Дм" sheetId="30" r:id="rId3"/>
+    <sheet name="5.2Рез" sheetId="29" r:id="rId4"/>
+    <sheet name="5.1Шлф" sheetId="24" r:id="rId5"/>
     <sheet name="черновик 1-5" sheetId="16" r:id="rId6"/>
     <sheet name="общий" sheetId="1" r:id="rId7"/>
-    <sheet name="4.1шпИнв" sheetId="15" r:id="rId8"/>
-    <sheet name="3.4ГВЛинв5э" sheetId="23" r:id="rId9"/>
-    <sheet name="3.3ГВЛинв" sheetId="22" r:id="rId10"/>
-    <sheet name="3.2штИнв" sheetId="21" r:id="rId11"/>
-    <sheet name="3.1штИнв" sheetId="14" r:id="rId12"/>
-    <sheet name="№1" sheetId="12" r:id="rId13"/>
-    <sheet name="№2" sheetId="13" r:id="rId14"/>
-    <sheet name="1.1.1" sheetId="9" r:id="rId15"/>
-    <sheet name="1.2.1" sheetId="2" r:id="rId16"/>
-    <sheet name="1.2.2" sheetId="3" r:id="rId17"/>
-    <sheet name="1.3.1" sheetId="4" r:id="rId18"/>
-    <sheet name="1.3.2" sheetId="7" r:id="rId19"/>
-    <sheet name="1.4.1" sheetId="6" r:id="rId20"/>
-    <sheet name="1.4.2" sheetId="10" r:id="rId21"/>
-    <sheet name="1.5.1" sheetId="8" r:id="rId22"/>
+    <sheet name="4.2шпИнв" sheetId="28" r:id="rId8"/>
+    <sheet name="4.1шпИнв" sheetId="15" r:id="rId9"/>
+    <sheet name="3.5штИнв" sheetId="26" r:id="rId10"/>
+    <sheet name="3.4ГВЛинв5э" sheetId="23" r:id="rId11"/>
+    <sheet name="3.3ГВЛинв" sheetId="22" r:id="rId12"/>
+    <sheet name="3.2штИнв" sheetId="21" r:id="rId13"/>
+    <sheet name="3.1штИнв" sheetId="14" r:id="rId14"/>
+    <sheet name="2.6шт" sheetId="20" r:id="rId15"/>
+    <sheet name="2.5шт" sheetId="19" r:id="rId16"/>
+    <sheet name="2.4ГВЛ" sheetId="17" r:id="rId17"/>
+    <sheet name="1.6КрпИнвСент" sheetId="25" r:id="rId18"/>
+    <sheet name="№1" sheetId="12" r:id="rId19"/>
+    <sheet name="№2" sheetId="13" r:id="rId20"/>
+    <sheet name="1.1.1" sheetId="9" r:id="rId21"/>
+    <sheet name="1.2.1" sheetId="2" r:id="rId22"/>
+    <sheet name="1.2.2" sheetId="3" r:id="rId23"/>
+    <sheet name="1.3.1" sheetId="4" r:id="rId24"/>
+    <sheet name="1.3.2" sheetId="7" r:id="rId25"/>
+    <sheet name="1.4.1" sheetId="6" r:id="rId26"/>
+    <sheet name="1.4.2" sheetId="10" r:id="rId27"/>
+    <sheet name="1.5.1" sheetId="8" r:id="rId28"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2536" uniqueCount="929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2834" uniqueCount="1025">
   <si>
     <t>Указать название организации (на бланке организации)</t>
   </si>
@@ -2830,6 +2836,299 @@
     <t>Шлифование бетонных поверхностей
 стен (снятие наплывов и швов, снятие
 цементного молочка)</t>
+  </si>
+  <si>
+    <t>Тип-1
+4-5 этаж</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Устройство перегородок из полнотелого одинарного керамического кирпича толщиной 120 мм, на растворе М125 с армированием сетками из арматуры ø4Вр-1 (B500) с ячейками 50х50 
+</t>
+  </si>
+  <si>
+    <t>4-5 этаж</t>
+  </si>
+  <si>
+    <t>Штукатурка стен цементным, цементно-песчаным раствором с предварительной огрунтовкой / толщ. 40 мм</t>
+  </si>
+  <si>
+    <t>подвал</t>
+  </si>
+  <si>
+    <t>подвал, 1 этаж
+базовая шпаклевка</t>
+  </si>
+  <si>
+    <t>краска</t>
+  </si>
+  <si>
+    <t>фартук плитка</t>
+  </si>
+  <si>
+    <t>фотообои</t>
+  </si>
+  <si>
+    <t>плитка</t>
+  </si>
+  <si>
+    <t>013а</t>
+  </si>
+  <si>
+    <t>013б</t>
+  </si>
+  <si>
+    <t>014а</t>
+  </si>
+  <si>
+    <t>014б</t>
+  </si>
+  <si>
+    <t>№ пом.</t>
+  </si>
+  <si>
+    <t>Площадь стен, м²</t>
+  </si>
+  <si>
+    <t>Тип отделки</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>020</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>028а</t>
+  </si>
+  <si>
+    <t>028б</t>
+  </si>
+  <si>
+    <t>029а</t>
+  </si>
+  <si>
+    <t>029б</t>
+  </si>
+  <si>
+    <t>034а</t>
+  </si>
+  <si>
+    <t>034б</t>
+  </si>
+  <si>
+    <t>035а</t>
+  </si>
+  <si>
+    <t>035б</t>
+  </si>
+  <si>
+    <t>036а</t>
+  </si>
+  <si>
+    <t>036б</t>
+  </si>
+  <si>
+    <t>037а</t>
+  </si>
+  <si>
+    <t>037б</t>
+  </si>
+  <si>
+    <t>023</t>
+  </si>
+  <si>
+    <t>024</t>
+  </si>
+  <si>
+    <t>025</t>
+  </si>
+  <si>
+    <t>026</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>028</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>032</t>
+  </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>045а</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>048</t>
+  </si>
+  <si>
+    <t>049</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>№ лш.</t>
+  </si>
+  <si>
+    <t>подвал,
+1-5 этаж</t>
+  </si>
+  <si>
+    <t>объем, пог. м.</t>
+  </si>
+  <si>
+    <t>Демонтаж бетона с сохранением арматуры</t>
+  </si>
+  <si>
+    <t>цена</t>
+  </si>
+  <si>
+    <t>алм резка</t>
+  </si>
+  <si>
+    <t>демонт</t>
+  </si>
+  <si>
+    <t>шлиф</t>
+  </si>
+  <si>
+    <t>объем</t>
+  </si>
+  <si>
+    <t>уборка</t>
+  </si>
+  <si>
+    <t>объем, м3.
+h = 0,1 м</t>
+  </si>
+  <si>
+    <t>итог</t>
+  </si>
+  <si>
+    <t>Алмазная резка железобетонных конструкций (учтены расходные материалы)_ / 100 мм</t>
+  </si>
+  <si>
+    <t>пог. м.</t>
   </si>
 </sst>
 </file>
@@ -3291,7 +3590,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3567,6 +3866,36 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -3659,6 +3988,12 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3965,39 +4300,1300 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1:C113"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="88"/>
+    <col min="2" max="16384" width="8.88671875" style="77"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="88" t="s">
+        <v>943</v>
+      </c>
+      <c r="B1" s="77" t="s">
+        <v>944</v>
+      </c>
+      <c r="C1" s="77" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="88" t="s">
+        <v>946</v>
+      </c>
+      <c r="B2" s="77">
+        <v>21.25</v>
+      </c>
+      <c r="C2" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="88" t="s">
+        <v>946</v>
+      </c>
+      <c r="B3" s="77">
+        <v>123.87</v>
+      </c>
+      <c r="C3" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="88" t="s">
+        <v>947</v>
+      </c>
+      <c r="B4" s="77">
+        <v>77.209999999999994</v>
+      </c>
+      <c r="C4" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="88" t="s">
+        <v>947</v>
+      </c>
+      <c r="B5" s="77">
+        <v>495.25</v>
+      </c>
+      <c r="C5" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="88" t="s">
+        <v>948</v>
+      </c>
+      <c r="B6" s="77">
+        <v>77.209999999999994</v>
+      </c>
+      <c r="C6" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="88" t="s">
+        <v>948</v>
+      </c>
+      <c r="B7" s="77">
+        <v>495.25</v>
+      </c>
+      <c r="C7" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="88" t="s">
+        <v>949</v>
+      </c>
+      <c r="B8" s="77">
+        <v>5.25</v>
+      </c>
+      <c r="C8" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="88" t="s">
+        <v>949</v>
+      </c>
+      <c r="B9" s="77">
+        <v>30.67</v>
+      </c>
+      <c r="C9" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="88" t="s">
+        <v>950</v>
+      </c>
+      <c r="B10" s="77">
+        <v>399.64</v>
+      </c>
+      <c r="C10" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="88" t="s">
+        <v>951</v>
+      </c>
+      <c r="B11" s="77">
+        <v>399.64</v>
+      </c>
+      <c r="C11" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="88" t="s">
+        <v>952</v>
+      </c>
+      <c r="B12" s="77">
+        <v>399.64</v>
+      </c>
+      <c r="C12" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="88" t="s">
+        <v>953</v>
+      </c>
+      <c r="B13" s="77">
+        <v>399.64</v>
+      </c>
+      <c r="C13" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="88" t="s">
+        <v>954</v>
+      </c>
+      <c r="B14" s="77">
+        <v>520.66</v>
+      </c>
+      <c r="C14" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="88" t="s">
+        <v>955</v>
+      </c>
+      <c r="B15" s="77">
+        <v>37.51</v>
+      </c>
+      <c r="C15" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="88" t="s">
+        <v>955</v>
+      </c>
+      <c r="B16" s="77">
+        <v>42.31</v>
+      </c>
+      <c r="C16" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="88" t="s">
+        <v>955</v>
+      </c>
+      <c r="B17" s="77">
+        <v>8.18</v>
+      </c>
+      <c r="C17" s="77" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="88" t="s">
+        <v>955</v>
+      </c>
+      <c r="B18" s="77">
+        <v>22.92</v>
+      </c>
+      <c r="C18" s="77" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="88" t="s">
+        <v>956</v>
+      </c>
+      <c r="B19" s="77">
+        <v>520.66</v>
+      </c>
+      <c r="C19" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="88" t="s">
+        <v>957</v>
+      </c>
+      <c r="B20" s="77">
+        <v>526.5</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="88" t="s">
+        <v>958</v>
+      </c>
+      <c r="B21" s="77">
+        <v>520.66</v>
+      </c>
+      <c r="C21" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="88" t="s">
+        <v>939</v>
+      </c>
+      <c r="B22" s="77">
+        <v>101.49</v>
+      </c>
+      <c r="C22" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="88" t="s">
+        <v>939</v>
+      </c>
+      <c r="B23" s="77">
+        <v>73.739999999999995</v>
+      </c>
+      <c r="C23" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="88" t="s">
+        <v>940</v>
+      </c>
+      <c r="B24" s="77">
+        <v>69.209999999999994</v>
+      </c>
+      <c r="C24" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="88" t="s">
+        <v>940</v>
+      </c>
+      <c r="B25" s="77">
+        <v>19.89</v>
+      </c>
+      <c r="C25" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="88" t="s">
+        <v>959</v>
+      </c>
+      <c r="B26" s="77">
+        <v>520.66</v>
+      </c>
+      <c r="C26" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="88" t="s">
+        <v>941</v>
+      </c>
+      <c r="B27" s="77">
+        <v>101.49</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="88" t="s">
+        <v>941</v>
+      </c>
+      <c r="B28" s="77">
+        <v>73.739999999999995</v>
+      </c>
+      <c r="C28" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="88" t="s">
+        <v>942</v>
+      </c>
+      <c r="B29" s="77">
+        <v>69.209999999999994</v>
+      </c>
+      <c r="C29" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="88" t="s">
+        <v>942</v>
+      </c>
+      <c r="B30" s="77">
+        <v>19.89</v>
+      </c>
+      <c r="C30" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="88" t="s">
+        <v>960</v>
+      </c>
+      <c r="B31" s="77">
+        <v>59.68</v>
+      </c>
+      <c r="C31" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="88" t="s">
+        <v>960</v>
+      </c>
+      <c r="B32" s="77">
+        <v>3.48</v>
+      </c>
+      <c r="C32" s="77" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="88" t="s">
+        <v>960</v>
+      </c>
+      <c r="B33" s="77">
+        <v>30.93</v>
+      </c>
+      <c r="C33" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="88" t="s">
+        <v>961</v>
+      </c>
+      <c r="B34" s="77">
+        <v>230.29</v>
+      </c>
+      <c r="C34" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="88" t="s">
+        <v>962</v>
+      </c>
+      <c r="B35" s="77">
+        <v>11.63</v>
+      </c>
+      <c r="C35" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="88" t="s">
+        <v>963</v>
+      </c>
+      <c r="B36" s="77">
+        <v>526.5</v>
+      </c>
+      <c r="C36" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="88" t="s">
+        <v>964</v>
+      </c>
+      <c r="B37" s="77">
+        <v>526.5</v>
+      </c>
+      <c r="C37" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="88" t="s">
+        <v>965</v>
+      </c>
+      <c r="B38" s="77">
+        <v>156.56</v>
+      </c>
+      <c r="C38" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="88" t="s">
+        <v>965</v>
+      </c>
+      <c r="B39" s="77">
+        <v>65.67</v>
+      </c>
+      <c r="C39" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="88" t="s">
+        <v>966</v>
+      </c>
+      <c r="B40" s="77">
+        <v>156.56</v>
+      </c>
+      <c r="C40" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="88" t="s">
+        <v>966</v>
+      </c>
+      <c r="B41" s="77">
+        <v>65.67</v>
+      </c>
+      <c r="C41" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="88" t="s">
+        <v>967</v>
+      </c>
+      <c r="B42" s="77">
+        <v>526.5</v>
+      </c>
+      <c r="C42" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="88" t="s">
+        <v>980</v>
+      </c>
+      <c r="B43" s="77">
+        <v>156.56</v>
+      </c>
+      <c r="C43" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="88" t="s">
+        <v>980</v>
+      </c>
+      <c r="B44" s="77">
+        <v>65.67</v>
+      </c>
+      <c r="C44" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="88" t="s">
+        <v>981</v>
+      </c>
+      <c r="B45" s="77">
+        <v>230.29</v>
+      </c>
+      <c r="C45" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="88" t="s">
+        <v>982</v>
+      </c>
+      <c r="B46" s="77">
+        <v>399.64</v>
+      </c>
+      <c r="C46" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="88" t="s">
+        <v>983</v>
+      </c>
+      <c r="B47" s="77">
+        <v>59.69</v>
+      </c>
+      <c r="C47" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="88" t="s">
+        <v>983</v>
+      </c>
+      <c r="B48" s="77">
+        <v>9.65</v>
+      </c>
+      <c r="C48" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="88" t="s">
+        <v>984</v>
+      </c>
+      <c r="B49" s="77">
+        <v>526.5</v>
+      </c>
+      <c r="C49" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="88" t="s">
+        <v>985</v>
+      </c>
+      <c r="B50" s="77">
+        <v>520.66</v>
+      </c>
+      <c r="C50" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="88" t="s">
+        <v>968</v>
+      </c>
+      <c r="B51" s="77">
+        <v>101.49</v>
+      </c>
+      <c r="C51" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="88" t="s">
+        <v>968</v>
+      </c>
+      <c r="B52" s="77">
+        <v>73.739999999999995</v>
+      </c>
+      <c r="C52" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="88" t="s">
+        <v>969</v>
+      </c>
+      <c r="B53" s="77">
+        <v>69.209999999999994</v>
+      </c>
+      <c r="C53" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="88" t="s">
+        <v>969</v>
+      </c>
+      <c r="B54" s="77">
+        <v>19.89</v>
+      </c>
+      <c r="C54" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="88" t="s">
+        <v>986</v>
+      </c>
+      <c r="B55" s="77">
+        <v>520.66</v>
+      </c>
+      <c r="C55" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="88" t="s">
+        <v>970</v>
+      </c>
+      <c r="B56" s="77">
+        <v>101.49</v>
+      </c>
+      <c r="C56" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="88" t="s">
+        <v>970</v>
+      </c>
+      <c r="B57" s="77">
+        <v>73.739999999999995</v>
+      </c>
+      <c r="C57" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="88" t="s">
+        <v>971</v>
+      </c>
+      <c r="B58" s="77">
+        <v>69.209999999999994</v>
+      </c>
+      <c r="C58" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="88" t="s">
+        <v>971</v>
+      </c>
+      <c r="B59" s="77">
+        <v>19.89</v>
+      </c>
+      <c r="C59" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="88" t="s">
+        <v>987</v>
+      </c>
+      <c r="B60" s="77">
+        <v>101.49</v>
+      </c>
+      <c r="C60" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="88" t="s">
+        <v>987</v>
+      </c>
+      <c r="B61" s="77">
+        <v>73.739999999999995</v>
+      </c>
+      <c r="C61" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="88" t="s">
+        <v>988</v>
+      </c>
+      <c r="B62" s="77">
+        <v>526.5</v>
+      </c>
+      <c r="C62" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="88" t="s">
+        <v>989</v>
+      </c>
+      <c r="B63" s="77">
+        <v>77.209999999999994</v>
+      </c>
+      <c r="C63" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="88" t="s">
+        <v>989</v>
+      </c>
+      <c r="B64" s="77">
+        <v>495.25</v>
+      </c>
+      <c r="C64" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="88" t="s">
+        <v>990</v>
+      </c>
+      <c r="B65" s="77">
+        <v>526.5</v>
+      </c>
+      <c r="C65" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="88" t="s">
+        <v>991</v>
+      </c>
+      <c r="B66" s="77">
+        <v>520.66</v>
+      </c>
+      <c r="C66" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="88" t="s">
+        <v>972</v>
+      </c>
+      <c r="B67" s="77">
+        <v>101.49</v>
+      </c>
+      <c r="C67" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="88" t="s">
+        <v>972</v>
+      </c>
+      <c r="B68" s="77">
+        <v>73.739999999999995</v>
+      </c>
+      <c r="C68" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="88" t="s">
+        <v>973</v>
+      </c>
+      <c r="B69" s="77">
+        <v>10.99</v>
+      </c>
+      <c r="C69" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="88" t="s">
+        <v>973</v>
+      </c>
+      <c r="B70" s="77">
+        <v>3.24</v>
+      </c>
+      <c r="C70" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="88" t="s">
+        <v>973</v>
+      </c>
+      <c r="B71" s="77">
+        <v>0.18</v>
+      </c>
+      <c r="C71" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="88" t="s">
+        <v>992</v>
+      </c>
+      <c r="B72" s="77">
+        <v>520.66</v>
+      </c>
+      <c r="C72" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="88" t="s">
+        <v>974</v>
+      </c>
+      <c r="B73" s="77">
+        <v>101.49</v>
+      </c>
+      <c r="C73" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="88" t="s">
+        <v>974</v>
+      </c>
+      <c r="B74" s="77">
+        <v>73.739999999999995</v>
+      </c>
+      <c r="C74" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="88" t="s">
+        <v>975</v>
+      </c>
+      <c r="B75" s="77">
+        <v>69.209999999999994</v>
+      </c>
+      <c r="C75" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="88" t="s">
+        <v>975</v>
+      </c>
+      <c r="B76" s="77">
+        <v>19.89</v>
+      </c>
+      <c r="C76" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="88" t="s">
+        <v>993</v>
+      </c>
+      <c r="B77" s="77">
+        <v>520.66</v>
+      </c>
+      <c r="C77" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="88" t="s">
+        <v>976</v>
+      </c>
+      <c r="B78" s="77">
+        <v>101.49</v>
+      </c>
+      <c r="C78" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="88" t="s">
+        <v>976</v>
+      </c>
+      <c r="B79" s="77">
+        <v>73.739999999999995</v>
+      </c>
+      <c r="C79" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="88" t="s">
+        <v>977</v>
+      </c>
+      <c r="B80" s="77">
+        <v>69.209999999999994</v>
+      </c>
+      <c r="C80" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="88" t="s">
+        <v>977</v>
+      </c>
+      <c r="B81" s="77">
+        <v>19.89</v>
+      </c>
+      <c r="C81" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="88" t="s">
+        <v>994</v>
+      </c>
+      <c r="B82" s="77">
+        <v>520.66</v>
+      </c>
+      <c r="C82" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="88" t="s">
+        <v>978</v>
+      </c>
+      <c r="B83" s="77">
+        <v>101.49</v>
+      </c>
+      <c r="C83" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="88" t="s">
+        <v>978</v>
+      </c>
+      <c r="B84" s="77">
+        <v>73.739999999999995</v>
+      </c>
+      <c r="C84" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="88" t="s">
+        <v>979</v>
+      </c>
+      <c r="B85" s="77">
+        <v>14.35</v>
+      </c>
+      <c r="C85" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="88" t="s">
+        <v>995</v>
+      </c>
+      <c r="B86" s="77">
+        <v>526.5</v>
+      </c>
+      <c r="C86" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="88" t="s">
+        <v>996</v>
+      </c>
+      <c r="B87" s="77">
+        <v>101.49</v>
+      </c>
+      <c r="C87" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="88" t="s">
+        <v>996</v>
+      </c>
+      <c r="B88" s="77">
+        <v>73.739999999999995</v>
+      </c>
+      <c r="C88" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="88" t="s">
+        <v>997</v>
+      </c>
+      <c r="B89" s="77">
+        <v>526.5</v>
+      </c>
+      <c r="C89" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="88" t="s">
+        <v>998</v>
+      </c>
+      <c r="B90" s="77">
+        <v>230.29</v>
+      </c>
+      <c r="C90" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="88" t="s">
+        <v>999</v>
+      </c>
+      <c r="B91" s="77">
+        <v>28.82</v>
+      </c>
+      <c r="C91" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="88" t="s">
+        <v>999</v>
+      </c>
+      <c r="B92" s="77">
+        <v>7.33</v>
+      </c>
+      <c r="C92" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="88" t="s">
+        <v>999</v>
+      </c>
+      <c r="B93" s="77">
+        <v>26.53</v>
+      </c>
+      <c r="C93" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="88" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B94" s="77">
+        <v>11.63</v>
+      </c>
+      <c r="C94" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="88" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B95" s="77">
+        <v>41.44</v>
+      </c>
+      <c r="C95" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="88" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B96" s="77">
+        <v>526.5</v>
+      </c>
+      <c r="C96" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="88" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B97" s="77">
+        <v>399.64</v>
+      </c>
+      <c r="C97" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="88" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B98" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C98" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="88" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B99" s="77">
+        <v>156.56</v>
+      </c>
+      <c r="C99" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="88" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B100" s="77">
+        <v>65.67</v>
+      </c>
+      <c r="C100" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="88" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B101" s="77">
+        <v>37.51</v>
+      </c>
+      <c r="C101" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="88" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B102" s="77">
+        <v>42.31</v>
+      </c>
+      <c r="C102" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="88" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B103" s="77">
+        <v>8.18</v>
+      </c>
+      <c r="C103" s="77" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="88" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B104" s="77">
+        <v>22.92</v>
+      </c>
+      <c r="C104" s="77" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="88" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B105" s="77">
+        <v>11.14</v>
+      </c>
+      <c r="C105" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="88" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B106" s="77">
+        <v>39.25</v>
+      </c>
+      <c r="C106" s="77" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="88" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B107" s="77">
+        <v>156.56</v>
+      </c>
+      <c r="C107" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="88" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B108" s="77">
+        <v>65.67</v>
+      </c>
+      <c r="C108" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="88" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B109" s="77">
+        <v>156.56</v>
+      </c>
+      <c r="C109" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="88" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B110" s="77">
+        <v>65.67</v>
+      </c>
+      <c r="C110" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="88" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B111" s="77">
+        <v>156.56</v>
+      </c>
+      <c r="C111" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="88" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B112" s="77">
+        <v>65.67</v>
+      </c>
+      <c r="C112" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="88" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B113" s="77">
+        <v>526.5</v>
+      </c>
+      <c r="C113" s="77" t="s">
+        <v>938</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.88671875" customWidth="1"/>
     <col min="3" max="3" width="6.33203125" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="106" t="s">
         <v>814</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="65" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="107" t="s">
         <v>816</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="93" t="s">
+      <c r="C2" s="108"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="97" t="s">
         <v>758</v>
       </c>
       <c r="F2" s="67" t="s">
@@ -4007,126 +5603,87 @@
         <v>817</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="92">
+    <row r="3" spans="1:7" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="96">
         <v>1</v>
       </c>
-      <c r="B3" s="100" t="s">
-        <v>928</v>
-      </c>
-      <c r="C3" s="101"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="94" t="s">
-        <v>829</v>
-      </c>
-      <c r="F3" s="92" t="s">
+      <c r="B3" s="110" t="s">
+        <v>932</v>
+      </c>
+      <c r="C3" s="111"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="98" t="s">
+        <v>931</v>
+      </c>
+      <c r="F3" s="96" t="s">
         <v>46</v>
       </c>
       <c r="G3" s="70">
-        <f>B11</f>
-        <v>4683.1000000000004</v>
+        <f>B8</f>
+        <v>566.47</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="103"/>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
     </row>
     <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="96" t="s">
         <v>831</v>
       </c>
-      <c r="B5" s="92" t="s">
+      <c r="B5" s="96" t="s">
         <v>821</v>
       </c>
-      <c r="C5" s="104"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="105"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="92">
-        <v>1</v>
+      <c r="A6" s="96">
+        <v>4</v>
       </c>
       <c r="B6" s="70">
-        <v>897.3</v>
-      </c>
-      <c r="C6" s="104"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="105"/>
+        <v>296.39999999999998</v>
+      </c>
+      <c r="C6" s="114"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="92">
-        <v>2</v>
+      <c r="A7" s="96">
+        <v>5</v>
       </c>
       <c r="B7" s="70">
-        <v>903.4</v>
-      </c>
-      <c r="C7" s="104"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
+        <v>270.07</v>
+      </c>
+      <c r="C7" s="114"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="115"/>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="92">
-        <v>3</v>
+      <c r="A8" s="99" t="s">
+        <v>828</v>
       </c>
       <c r="B8" s="70">
-        <v>902.4</v>
-      </c>
-      <c r="C8" s="104"/>
-      <c r="D8" s="105"/>
-      <c r="E8" s="105"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="105"/>
-    </row>
-    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="92">
-        <v>4</v>
-      </c>
-      <c r="B9" s="70">
-        <v>1001.4</v>
-      </c>
-      <c r="C9" s="104"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-      <c r="G9" s="105"/>
-    </row>
-    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="92">
-        <v>5</v>
-      </c>
-      <c r="B10" s="70">
-        <v>978.6</v>
-      </c>
-      <c r="C10" s="104"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="105"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="95" t="s">
-        <v>828</v>
-      </c>
-      <c r="B11" s="70">
-        <f>SUM(B6:B10)</f>
-        <v>4683.1000000000004</v>
-      </c>
-      <c r="C11" s="104"/>
-      <c r="D11" s="105"/>
-      <c r="E11" s="105"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="105"/>
+        <f>SUM(B6:B7)</f>
+        <v>566.47</v>
+      </c>
+      <c r="C8" s="114"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="115"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4134,13 +5691,214 @@
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="C5:G11"/>
+    <mergeCell ref="C5:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="56.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>757</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>758</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="60" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.3">
+      <c r="A2" s="42">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>759</v>
+      </c>
+      <c r="E2" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="59">
+        <v>382.23900000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="42">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="59">
+        <v>12.4245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="42">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="8">
+        <v>30.492000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="42">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="8">
+        <v>4.0179999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="42">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="8">
+        <v>150.52799999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="42">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="8">
+        <v>15.617000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="54" x14ac:dyDescent="0.3">
+      <c r="A8" s="42">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="8">
+        <v>18.769500000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="42">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="8">
+        <v>5.3835000000000006</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -4321,7 +6079,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4336,25 +6094,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="106" t="s">
         <v>814</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
     </row>
     <row r="2" spans="1:7" s="77" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="89" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="137" t="s">
         <v>816</v>
       </c>
-      <c r="C2" s="129"/>
-      <c r="D2" s="128"/>
+      <c r="C2" s="139"/>
+      <c r="D2" s="138"/>
       <c r="E2" s="91" t="s">
         <v>758</v>
       </c>
@@ -4369,11 +6127,11 @@
       <c r="A3" s="89">
         <v>1</v>
       </c>
-      <c r="B3" s="100" t="s">
+      <c r="B3" s="110" t="s">
         <v>439</v>
       </c>
-      <c r="C3" s="101"/>
-      <c r="D3" s="102"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="112"/>
       <c r="E3" s="90" t="s">
         <v>927</v>
       </c>
@@ -4394,7 +6152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист6"/>
   <dimension ref="A1:L72"/>
@@ -4410,25 +6168,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="106" t="s">
         <v>814</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
     </row>
     <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="65" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="107" t="s">
         <v>816</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="99"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="109"/>
       <c r="E2" s="66" t="s">
         <v>758</v>
       </c>
@@ -4443,11 +6201,11 @@
       <c r="A3" s="68">
         <v>1</v>
       </c>
-      <c r="B3" s="100" t="s">
+      <c r="B3" s="110" t="s">
         <v>439</v>
       </c>
-      <c r="C3" s="101"/>
-      <c r="D3" s="102"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="112"/>
       <c r="E3" s="69" t="s">
         <v>829</v>
       </c>
@@ -4460,13 +6218,13 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="103"/>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
     </row>
     <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="68" t="s">
@@ -4475,11 +6233,11 @@
       <c r="B5" s="68" t="s">
         <v>821</v>
       </c>
-      <c r="C5" s="104"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="105"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
     </row>
     <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="68">
@@ -4488,11 +6246,11 @@
       <c r="B6" s="70">
         <v>752.48</v>
       </c>
-      <c r="C6" s="104"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="105"/>
+      <c r="C6" s="114"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
     </row>
     <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="68">
@@ -4501,11 +6259,11 @@
       <c r="B7" s="70">
         <v>806</v>
       </c>
-      <c r="C7" s="104"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="115"/>
     </row>
     <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="68">
@@ -4514,11 +6272,11 @@
       <c r="B8" s="70">
         <v>788.8</v>
       </c>
-      <c r="C8" s="104"/>
-      <c r="D8" s="105"/>
-      <c r="E8" s="105"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="105"/>
+      <c r="C8" s="114"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="115"/>
     </row>
     <row r="9" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="68">
@@ -4527,11 +6285,11 @@
       <c r="B9" s="70">
         <v>788.8</v>
       </c>
-      <c r="C9" s="104"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-      <c r="G9" s="105"/>
+      <c r="C9" s="114"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
     </row>
     <row r="10" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="68">
@@ -4540,11 +6298,11 @@
       <c r="B10" s="70">
         <v>610.4</v>
       </c>
-      <c r="C10" s="104"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="105"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="115"/>
     </row>
     <row r="11" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="74" t="s">
@@ -4554,11 +6312,11 @@
         <f>SUM(B6:B10)</f>
         <v>3746.48</v>
       </c>
-      <c r="C11" s="104"/>
-      <c r="D11" s="105"/>
-      <c r="E11" s="105"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="105"/>
+      <c r="C11" s="114"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="115"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="115"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H15" s="77">
@@ -5032,7 +6790,578 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="106" t="s">
+        <v>814</v>
+      </c>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
+        <v>815</v>
+      </c>
+      <c r="B2" s="107" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2" s="108"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="83" t="s">
+        <v>758</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="67" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="82">
+        <v>1</v>
+      </c>
+      <c r="B3" s="110" t="s">
+        <v>439</v>
+      </c>
+      <c r="C3" s="111"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="84" t="s">
+        <v>926</v>
+      </c>
+      <c r="F3" s="82" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="70">
+        <v>1959.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="82" t="s">
+        <v>831</v>
+      </c>
+      <c r="B5" s="82" t="s">
+        <v>821</v>
+      </c>
+      <c r="C5" s="114"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="82">
+        <v>-1</v>
+      </c>
+      <c r="B6" s="70">
+        <v>1959.9</v>
+      </c>
+      <c r="C6" s="114"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="85" t="s">
+        <v>828</v>
+      </c>
+      <c r="B7" s="70">
+        <f>SUM(B6:B6)</f>
+        <v>1959.9</v>
+      </c>
+      <c r="C7" s="114"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="115"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="C5:G7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист17"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="106" t="s">
+        <v>814</v>
+      </c>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
+        <v>815</v>
+      </c>
+      <c r="B2" s="107" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2" s="108"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="79" t="s">
+        <v>758</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="67" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="78">
+        <v>1</v>
+      </c>
+      <c r="B3" s="110" t="s">
+        <v>439</v>
+      </c>
+      <c r="C3" s="111"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="80" t="s">
+        <v>829</v>
+      </c>
+      <c r="F3" s="78" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="70">
+        <f>B11</f>
+        <v>4716.6000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="78" t="s">
+        <v>831</v>
+      </c>
+      <c r="B5" s="78" t="s">
+        <v>821</v>
+      </c>
+      <c r="C5" s="114"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="78">
+        <v>1</v>
+      </c>
+      <c r="B6" s="70">
+        <v>905.8</v>
+      </c>
+      <c r="C6" s="114"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="78">
+        <v>2</v>
+      </c>
+      <c r="B7" s="70">
+        <v>911.4</v>
+      </c>
+      <c r="C7" s="114"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="115"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="78">
+        <v>3</v>
+      </c>
+      <c r="B8" s="70">
+        <v>905.40000000000009</v>
+      </c>
+      <c r="C8" s="114"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="115"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="78">
+        <v>4</v>
+      </c>
+      <c r="B9" s="70">
+        <v>1005.4000000000001</v>
+      </c>
+      <c r="C9" s="114"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="78">
+        <v>5</v>
+      </c>
+      <c r="B10" s="70">
+        <v>988.60000000000014</v>
+      </c>
+      <c r="C10" s="114"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="115"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="81" t="s">
+        <v>828</v>
+      </c>
+      <c r="B11" s="70">
+        <f>SUM(B6:B10)</f>
+        <v>4716.6000000000004</v>
+      </c>
+      <c r="C11" s="114"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="115"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="115"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="C5:G11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист2">
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="56.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="6" max="8" width="16.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>757</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>758</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="60" t="s">
+        <v>813</v>
+      </c>
+      <c r="H1" s="60" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="42">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="59">
+        <f t="shared" ref="F2:F4" si="0">SUM(G2:H2)</f>
+        <v>247.184</v>
+      </c>
+      <c r="G2" s="8">
+        <v>186.2</v>
+      </c>
+      <c r="H2" s="8">
+        <v>60.984000000000009</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="42">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="59">
+        <f>SUM(G3:H3)</f>
+        <v>49.534000000000006</v>
+      </c>
+      <c r="G3" s="8">
+        <v>18.3</v>
+      </c>
+      <c r="H3" s="8">
+        <v>31.234000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="42">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="59">
+        <f t="shared" si="0"/>
+        <v>28.867000000000004</v>
+      </c>
+      <c r="G4" s="8">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="H4" s="8">
+        <v>10.767000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" customWidth="1"/>
+    <col min="4" max="4" width="27.88671875" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="106" t="s">
+        <v>814</v>
+      </c>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
+        <v>815</v>
+      </c>
+      <c r="B2" s="107" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2" s="108"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="97" t="s">
+        <v>758</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="67" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="96">
+        <v>1</v>
+      </c>
+      <c r="B3" s="110" t="s">
+        <v>930</v>
+      </c>
+      <c r="C3" s="111"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="98" t="s">
+        <v>929</v>
+      </c>
+      <c r="F3" s="96" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="70">
+        <f>B8</f>
+        <v>384.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="96" t="s">
+        <v>831</v>
+      </c>
+      <c r="B5" s="96" t="s">
+        <v>821</v>
+      </c>
+      <c r="C5" s="114"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="96">
+        <v>4</v>
+      </c>
+      <c r="B6" s="70">
+        <v>189.5</v>
+      </c>
+      <c r="C6" s="114"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="96">
+        <v>5</v>
+      </c>
+      <c r="B7" s="70">
+        <v>194.7</v>
+      </c>
+      <c r="C7" s="114"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="115"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="99" t="s">
+        <v>828</v>
+      </c>
+      <c r="B8" s="70">
+        <f>SUM(B6:B7)</f>
+        <v>384.2</v>
+      </c>
+      <c r="C8" s="114"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="115"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="C5:G8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист7">
     <tabColor rgb="FF92D050"/>
@@ -5262,7 +7591,1424 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист1">
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1:L90"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="88"/>
+    <col min="2" max="4" width="13.88671875" style="77" customWidth="1"/>
+    <col min="5" max="7" width="8.88671875" style="77"/>
+    <col min="8" max="8" width="10.6640625" style="77" customWidth="1"/>
+    <col min="9" max="10" width="8.88671875" style="77"/>
+    <col min="11" max="11" width="12.109375" style="77" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="77"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="87" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="86" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1" s="87" t="s">
+        <v>895</v>
+      </c>
+      <c r="C1" s="87" t="s">
+        <v>896</v>
+      </c>
+      <c r="D1" s="87" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="88" t="s">
+        <v>854</v>
+      </c>
+      <c r="B2" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C2" s="77">
+        <v>54.2</v>
+      </c>
+      <c r="D2" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="88" t="s">
+        <v>855</v>
+      </c>
+      <c r="B3" s="77">
+        <v>45.03</v>
+      </c>
+      <c r="C3" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D3" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="G3" s="77">
+        <v>0</v>
+      </c>
+      <c r="H3" s="77">
+        <v>1</v>
+      </c>
+      <c r="I3" s="77">
+        <v>2</v>
+      </c>
+      <c r="J3" s="77">
+        <v>3</v>
+      </c>
+      <c r="K3" s="77">
+        <v>4</v>
+      </c>
+      <c r="L3" s="77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="88" t="s">
+        <v>856</v>
+      </c>
+      <c r="B4" s="77">
+        <v>278.32</v>
+      </c>
+      <c r="C4" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D4" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="G4" s="77">
+        <v>1749</v>
+      </c>
+      <c r="H4" s="77">
+        <v>11.7</v>
+      </c>
+      <c r="I4" s="77">
+        <v>86.7</v>
+      </c>
+      <c r="J4" s="77">
+        <v>170.3</v>
+      </c>
+      <c r="K4" s="77">
+        <v>174.1</v>
+      </c>
+      <c r="L4" s="77">
+        <v>728.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="88" t="s">
+        <v>857</v>
+      </c>
+      <c r="B5" s="77">
+        <v>29.72</v>
+      </c>
+      <c r="C5" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D5" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="G5" s="77">
+        <v>254.2</v>
+      </c>
+      <c r="H5" s="77">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="I5" s="77">
+        <v>481.4</v>
+      </c>
+      <c r="J5" s="77">
+        <v>397.6</v>
+      </c>
+      <c r="K5" s="77">
+        <v>407.6</v>
+      </c>
+      <c r="L5" s="77">
+        <v>198.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="88" t="s">
+        <v>839</v>
+      </c>
+      <c r="B6" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C6" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D6" s="77">
+        <v>144.29</v>
+      </c>
+      <c r="G6" s="77">
+        <v>910.3</v>
+      </c>
+      <c r="H6" s="77">
+        <v>279.7</v>
+      </c>
+      <c r="I6" s="77">
+        <v>286</v>
+      </c>
+      <c r="J6" s="77">
+        <v>277</v>
+      </c>
+      <c r="K6" s="77">
+        <v>366.9</v>
+      </c>
+      <c r="L6" s="77">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="88" t="s">
+        <v>858</v>
+      </c>
+      <c r="B7" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C7" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D7" s="77">
+        <v>144.29</v>
+      </c>
+      <c r="G7" s="77">
+        <v>11.2</v>
+      </c>
+      <c r="H7" s="77">
+        <v>456</v>
+      </c>
+      <c r="I7" s="77">
+        <v>57.3</v>
+      </c>
+      <c r="J7" s="77">
+        <v>60.5</v>
+      </c>
+      <c r="K7" s="77">
+        <v>43.2</v>
+      </c>
+      <c r="L7" s="77">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="88" t="s">
+        <v>859</v>
+      </c>
+      <c r="B8" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C8" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D8" s="77">
+        <v>144.29</v>
+      </c>
+      <c r="H8" s="77">
+        <v>76.5</v>
+      </c>
+      <c r="K8" s="77">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="88" t="s">
+        <v>860</v>
+      </c>
+      <c r="B9" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C9" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D9" s="77">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="88" t="s">
+        <v>861</v>
+      </c>
+      <c r="B10" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C10" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D10" s="77">
+        <v>253.19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="88" t="s">
+        <v>862</v>
+      </c>
+      <c r="B11" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C11" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D11" s="77">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="88" t="s">
+        <v>863</v>
+      </c>
+      <c r="B12" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C12" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D12" s="77">
+        <v>253.19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="88" t="s">
+        <v>864</v>
+      </c>
+      <c r="B13" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C13" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D13" s="77">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="88" t="s">
+        <v>865</v>
+      </c>
+      <c r="B14" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C14" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D14" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="88" t="s">
+        <v>840</v>
+      </c>
+      <c r="B15" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C15" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D15" s="77">
+        <v>33.53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="88" t="s">
+        <v>866</v>
+      </c>
+      <c r="B16" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C16" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D16" s="77">
+        <v>17.09</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="88" t="s">
+        <v>867</v>
+      </c>
+      <c r="B17" s="77">
+        <v>31.06</v>
+      </c>
+      <c r="C17" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D17" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="88" t="s">
+        <v>868</v>
+      </c>
+      <c r="B18" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C18" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D18" s="77">
+        <v>12.67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="88" t="s">
+        <v>869</v>
+      </c>
+      <c r="B19" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C19" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D19" s="77">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="88" t="s">
+        <v>870</v>
+      </c>
+      <c r="B20" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D20" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="88" t="s">
+        <v>841</v>
+      </c>
+      <c r="B21" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C21" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D21" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="88" t="s">
+        <v>842</v>
+      </c>
+      <c r="B22" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C22" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D22" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="88" t="s">
+        <v>843</v>
+      </c>
+      <c r="B23" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C23" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D23" s="77">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="88" t="s">
+        <v>871</v>
+      </c>
+      <c r="B24" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C24" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D24" s="77">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="88" t="s">
+        <v>872</v>
+      </c>
+      <c r="B25" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C25" s="77">
+        <v>54.2</v>
+      </c>
+      <c r="D25" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="88" t="s">
+        <v>873</v>
+      </c>
+      <c r="B26" s="77">
+        <v>32.130000000000003</v>
+      </c>
+      <c r="C26" s="77">
+        <v>17.690000000000001</v>
+      </c>
+      <c r="D26" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="88" t="s">
+        <v>874</v>
+      </c>
+      <c r="B27" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D27" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="88" t="s">
+        <v>844</v>
+      </c>
+      <c r="B28" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C28" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D28" s="77">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="88" t="s">
+        <v>875</v>
+      </c>
+      <c r="B29" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C29" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D29" s="77">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="88" t="s">
+        <v>876</v>
+      </c>
+      <c r="B30" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C30" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D30" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="88" t="s">
+        <v>845</v>
+      </c>
+      <c r="B31" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C31" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D31" s="77">
+        <v>253.19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="88" t="s">
+        <v>877</v>
+      </c>
+      <c r="B32" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C32" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D32" s="77">
+        <v>109.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="88" t="s">
+        <v>878</v>
+      </c>
+      <c r="B33" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C33" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D33" s="77">
+        <v>33.53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="88" t="s">
+        <v>879</v>
+      </c>
+      <c r="B34" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C34" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D34" s="77">
+        <v>9.6300000000000008</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="88" t="s">
+        <v>880</v>
+      </c>
+      <c r="B35" s="77">
+        <v>278.32</v>
+      </c>
+      <c r="C35" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D35" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="88" t="s">
+        <v>881</v>
+      </c>
+      <c r="B36" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C36" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D36" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="88" t="s">
+        <v>846</v>
+      </c>
+      <c r="B37" s="77">
+        <v>24.96</v>
+      </c>
+      <c r="C37" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D37" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="88" t="s">
+        <v>882</v>
+      </c>
+      <c r="B38" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C38" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D38" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="88" t="s">
+        <v>847</v>
+      </c>
+      <c r="B39" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C39" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D39" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="88" t="s">
+        <v>848</v>
+      </c>
+      <c r="B40" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C40" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D40" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="88" t="s">
+        <v>849</v>
+      </c>
+      <c r="B41" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C41" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D41" s="77">
+        <v>253.19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="88" t="s">
+        <v>883</v>
+      </c>
+      <c r="B42" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C42" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D42" s="77">
+        <v>109.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="88" t="s">
+        <v>884</v>
+      </c>
+      <c r="B43" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C43" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D43" s="77">
+        <v>33.53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="88" t="s">
+        <v>885</v>
+      </c>
+      <c r="B44" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C44" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D44" s="77">
+        <v>9.6300000000000008</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="88" t="s">
+        <v>886</v>
+      </c>
+      <c r="B45" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C45" s="77">
+        <v>110.62</v>
+      </c>
+      <c r="D45" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="88" t="s">
+        <v>887</v>
+      </c>
+      <c r="B46" s="77">
+        <v>45.03</v>
+      </c>
+      <c r="C46" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D46" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="88" t="s">
+        <v>888</v>
+      </c>
+      <c r="B47" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C47" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D47" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="88" t="s">
+        <v>850</v>
+      </c>
+      <c r="B48" s="77">
+        <v>5.44</v>
+      </c>
+      <c r="C48" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D48" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="88" t="s">
+        <v>889</v>
+      </c>
+      <c r="B49" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C49" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D49" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="88" t="s">
+        <v>851</v>
+      </c>
+      <c r="B50" s="77">
+        <v>31.06</v>
+      </c>
+      <c r="C50" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D50" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="88" t="s">
+        <v>852</v>
+      </c>
+      <c r="B51" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C51" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D51" s="77">
+        <v>109.3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="88" t="s">
+        <v>890</v>
+      </c>
+      <c r="B52" s="77">
+        <v>14.17</v>
+      </c>
+      <c r="C52" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D52" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="88" t="s">
+        <v>853</v>
+      </c>
+      <c r="B53" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C53" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D53" s="77">
+        <v>253.19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="88" t="s">
+        <v>891</v>
+      </c>
+      <c r="B54" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C54" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D54" s="77">
+        <v>253.19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="88" t="s">
+        <v>892</v>
+      </c>
+      <c r="B55" s="77">
+        <v>31.06</v>
+      </c>
+      <c r="C55" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D55" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="88" t="s">
+        <v>893</v>
+      </c>
+      <c r="B56" s="77">
+        <v>44.74</v>
+      </c>
+      <c r="C56" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D56" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="88" t="s">
+        <v>898</v>
+      </c>
+      <c r="B60" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C60" s="77">
+        <v>77.23</v>
+      </c>
+      <c r="D60" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="88" t="s">
+        <v>899</v>
+      </c>
+      <c r="B61" s="77">
+        <v>24.2</v>
+      </c>
+      <c r="C61" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D61" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="88" t="s">
+        <v>900</v>
+      </c>
+      <c r="B62" s="77">
+        <v>73.42</v>
+      </c>
+      <c r="C62" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D62" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="88" t="s">
+        <v>901</v>
+      </c>
+      <c r="B63" s="77">
+        <v>91.72</v>
+      </c>
+      <c r="C63" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D63" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="88" t="s">
+        <v>836</v>
+      </c>
+      <c r="B64" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C64" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D64" s="77">
+        <v>104.72</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65" s="88" t="s">
+        <v>837</v>
+      </c>
+      <c r="B65" s="77">
+        <v>234.98</v>
+      </c>
+      <c r="C65" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D65" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66" s="88" t="s">
+        <v>902</v>
+      </c>
+      <c r="B66" s="77">
+        <v>91.72</v>
+      </c>
+      <c r="C66" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D66" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67" s="88" t="s">
+        <v>903</v>
+      </c>
+      <c r="B67" s="77">
+        <v>91.72</v>
+      </c>
+      <c r="C67" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D67" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="88" t="s">
+        <v>904</v>
+      </c>
+      <c r="B68" s="77">
+        <v>56.51</v>
+      </c>
+      <c r="C68" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D68" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="J68" s="70">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="88" t="s">
+        <v>838</v>
+      </c>
+      <c r="B69" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C69" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D69" s="77">
+        <v>104.72</v>
+      </c>
+      <c r="J69" s="70">
+        <v>788.8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70" s="88" t="s">
+        <v>905</v>
+      </c>
+      <c r="B70" s="77">
+        <v>91.72</v>
+      </c>
+      <c r="C70" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D70" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" s="88" t="s">
+        <v>906</v>
+      </c>
+      <c r="B71" s="77">
+        <v>7.81</v>
+      </c>
+      <c r="C71" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D71" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72" s="88" t="s">
+        <v>907</v>
+      </c>
+      <c r="B72" s="77">
+        <v>91.72</v>
+      </c>
+      <c r="C72" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D72" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73" s="88" t="s">
+        <v>908</v>
+      </c>
+      <c r="B73" s="77">
+        <v>91.72</v>
+      </c>
+      <c r="C73" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D73" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" s="88" t="s">
+        <v>909</v>
+      </c>
+      <c r="B74" s="77">
+        <v>48.37</v>
+      </c>
+      <c r="C74" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D74" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75" s="88" t="s">
+        <v>910</v>
+      </c>
+      <c r="B75" s="77">
+        <v>29.8</v>
+      </c>
+      <c r="C75" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D75" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76" s="88" t="s">
+        <v>911</v>
+      </c>
+      <c r="B76" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C76" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D76" s="77">
+        <v>31.04</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77" s="88" t="s">
+        <v>912</v>
+      </c>
+      <c r="B77" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C77" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D77" s="77">
+        <v>104.72</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78" s="88" t="s">
+        <v>913</v>
+      </c>
+      <c r="B78" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C78" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D78" s="77">
+        <v>234.98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A79" s="88" t="s">
+        <v>914</v>
+      </c>
+      <c r="B79" s="77">
+        <v>18.579999999999998</v>
+      </c>
+      <c r="C79" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D79" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="I79" s="77" t="s">
+        <v>1019</v>
+      </c>
+      <c r="J79" s="77" t="s">
+        <v>1015</v>
+      </c>
+      <c r="K79" s="77" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A80" s="88" t="s">
+        <v>915</v>
+      </c>
+      <c r="B80" s="77">
+        <v>56.51</v>
+      </c>
+      <c r="C80" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D80" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="H80" s="77" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I80" s="77">
+        <f>'5.2Рез'!G3</f>
+        <v>1608</v>
+      </c>
+      <c r="J80" s="77">
+        <v>1412</v>
+      </c>
+      <c r="K80" s="141">
+        <f>I80*J80</f>
+        <v>2270496</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A81" s="88" t="s">
+        <v>916</v>
+      </c>
+      <c r="B81" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C81" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D81" s="77">
+        <v>234.98</v>
+      </c>
+      <c r="H81" s="77" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I81" s="77">
+        <f>'5.3Дм'!G3</f>
+        <v>12.9</v>
+      </c>
+      <c r="J81" s="77">
+        <v>6767</v>
+      </c>
+      <c r="K81" s="141">
+        <f t="shared" ref="K81:K83" si="0">I81*J81</f>
+        <v>87294.3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A82" s="88" t="s">
+        <v>917</v>
+      </c>
+      <c r="B82" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C82" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D82" s="77">
+        <v>234.98</v>
+      </c>
+      <c r="H82" s="77" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I82" s="77">
+        <v>779</v>
+      </c>
+      <c r="J82" s="77">
+        <v>371</v>
+      </c>
+      <c r="K82" s="141">
+        <f t="shared" si="0"/>
+        <v>289009</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A83" s="88" t="s">
+        <v>918</v>
+      </c>
+      <c r="B83" s="77">
+        <v>33.92</v>
+      </c>
+      <c r="C83" s="77">
+        <v>17.690000000000001</v>
+      </c>
+      <c r="D83" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="H83" s="77" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I83" s="77">
+        <f>I81</f>
+        <v>12.9</v>
+      </c>
+      <c r="J83" s="77">
+        <v>1127</v>
+      </c>
+      <c r="K83" s="141">
+        <f t="shared" si="0"/>
+        <v>14538.300000000001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A84" s="88" t="s">
+        <v>919</v>
+      </c>
+      <c r="B84" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C84" s="77">
+        <v>27.88</v>
+      </c>
+      <c r="D84" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="J84" s="77" t="s">
+        <v>1022</v>
+      </c>
+      <c r="K84" s="141">
+        <f>SUM(K80:K83)</f>
+        <v>2661337.5999999996</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A85" s="88" t="s">
+        <v>920</v>
+      </c>
+      <c r="B85" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C85" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D85" s="77">
+        <v>234.98</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A86" s="88" t="s">
+        <v>921</v>
+      </c>
+      <c r="B86" s="77">
+        <v>56.51</v>
+      </c>
+      <c r="C86" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D86" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A87" s="88" t="s">
+        <v>922</v>
+      </c>
+      <c r="B87" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C87" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D87" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A88" s="88" t="s">
+        <v>923</v>
+      </c>
+      <c r="B88" s="77">
+        <v>203.07</v>
+      </c>
+      <c r="C88" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D88" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A89" s="88" t="s">
+        <v>924</v>
+      </c>
+      <c r="B89" s="77">
+        <v>203.07</v>
+      </c>
+      <c r="C89" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D89" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A90" s="88" t="s">
+        <v>925</v>
+      </c>
+      <c r="B90" s="77">
+        <v>73.42</v>
+      </c>
+      <c r="C90" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D90" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист8">
     <tabColor rgb="FF00B050"/>
@@ -5524,7 +9270,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист9">
     <tabColor rgb="FF00B050"/>
@@ -5707,7 +9453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист10">
     <tabColor rgb="FF92D050"/>
@@ -5870,7 +9616,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист11"/>
   <dimension ref="A1:F2"/>
@@ -5931,7 +9677,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист12">
     <tabColor rgb="FF92D050"/>
@@ -6094,7 +9840,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист13"/>
   <dimension ref="A1:F2"/>
@@ -6155,131 +9901,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" customWidth="1"/>
-    <col min="3" max="3" width="6.33203125" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="96" t="s">
-        <v>814</v>
-      </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-    </row>
-    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="65" t="s">
-        <v>815</v>
-      </c>
-      <c r="B2" s="97" t="s">
-        <v>816</v>
-      </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="83" t="s">
-        <v>758</v>
-      </c>
-      <c r="F2" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="67" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="82">
-        <v>1</v>
-      </c>
-      <c r="B3" s="100" t="s">
-        <v>439</v>
-      </c>
-      <c r="C3" s="101"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="84" t="s">
-        <v>926</v>
-      </c>
-      <c r="F3" s="82" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="70">
-        <v>1959.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="103"/>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="82" t="s">
-        <v>831</v>
-      </c>
-      <c r="B5" s="82" t="s">
-        <v>821</v>
-      </c>
-      <c r="C5" s="104"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="105"/>
-    </row>
-    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="82">
-        <v>-1</v>
-      </c>
-      <c r="B6" s="70">
-        <v>1959.9</v>
-      </c>
-      <c r="C6" s="104"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="105"/>
-    </row>
-    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="85" t="s">
-        <v>828</v>
-      </c>
-      <c r="B7" s="70">
-        <f>SUM(B6:B6)</f>
-        <v>1959.9</v>
-      </c>
-      <c r="C7" s="104"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="C5:G7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист14">
     <tabColor rgb="FF92D050"/>
@@ -6442,7 +10064,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист15"/>
   <dimension ref="A1:F2"/>
@@ -6503,7 +10125,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист16">
     <tabColor rgb="FF00B050"/>
@@ -6708,7 +10330,351 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Лист17"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="4.21875" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="106" t="s">
+        <v>814</v>
+      </c>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
+        <v>815</v>
+      </c>
+      <c r="B2" s="107" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2" s="108"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="103" t="s">
+        <v>758</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="67" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="102">
+        <v>1</v>
+      </c>
+      <c r="B3" s="110" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C3" s="111"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="104" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F3" s="102" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="70">
+        <f>C10</f>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+    </row>
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="102" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B5" s="102" t="s">
+        <v>821</v>
+      </c>
+      <c r="C5" s="140" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D5" s="114"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="102">
+        <v>1</v>
+      </c>
+      <c r="B6" s="70">
+        <v>41.1</v>
+      </c>
+      <c r="C6" s="70">
+        <f>B6*0.1</f>
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="D6" s="114"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="102">
+        <v>2</v>
+      </c>
+      <c r="B7" s="70">
+        <v>30.3</v>
+      </c>
+      <c r="C7" s="70">
+        <f t="shared" ref="C7:C9" si="0">B7*0.1</f>
+        <v>3.0300000000000002</v>
+      </c>
+      <c r="D7" s="114"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="115"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="102">
+        <v>3</v>
+      </c>
+      <c r="B8" s="70">
+        <v>24.4</v>
+      </c>
+      <c r="C8" s="70">
+        <f t="shared" si="0"/>
+        <v>2.44</v>
+      </c>
+      <c r="D8" s="114"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="115"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="102">
+        <v>4</v>
+      </c>
+      <c r="B9" s="70">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="C9" s="70">
+        <f t="shared" si="0"/>
+        <v>3.3200000000000003</v>
+      </c>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="105" t="s">
+        <v>828</v>
+      </c>
+      <c r="B10" s="70">
+        <f>SUM(B6:B9)</f>
+        <v>129</v>
+      </c>
+      <c r="C10" s="70">
+        <f>SUM(C6:C9)</f>
+        <v>12.9</v>
+      </c>
+      <c r="D10" s="114"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="115"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D5:G10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="106" t="s">
+        <v>814</v>
+      </c>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
+        <v>815</v>
+      </c>
+      <c r="B2" s="107" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2" s="108"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="103" t="s">
+        <v>758</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="67" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="102">
+        <v>1</v>
+      </c>
+      <c r="B3" s="110" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C3" s="111"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="104" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F3" s="102" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G3" s="70">
+        <f>B10</f>
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="102" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B5" s="102" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C5" s="114"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="102">
+        <v>1</v>
+      </c>
+      <c r="B6" s="70">
+        <v>486.1</v>
+      </c>
+      <c r="C6" s="114"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="102">
+        <v>2</v>
+      </c>
+      <c r="B7" s="70">
+        <v>385.2</v>
+      </c>
+      <c r="C7" s="114"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="115"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="102">
+        <v>3</v>
+      </c>
+      <c r="B8" s="70">
+        <v>312.8</v>
+      </c>
+      <c r="C8" s="114"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="115"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="102">
+        <v>4</v>
+      </c>
+      <c r="B9" s="70">
+        <v>423.9</v>
+      </c>
+      <c r="C9" s="114"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="105" t="s">
+        <v>828</v>
+      </c>
+      <c r="B10" s="70">
+        <f>SUM(B6:B9)</f>
+        <v>1608</v>
+      </c>
+      <c r="C10" s="114"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="115"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="C5:G10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6722,26 +10688,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="106" t="s">
         <v>814</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="65" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="107" t="s">
         <v>816</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="79" t="s">
+      <c r="C2" s="108"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="93" t="s">
         <v>758</v>
       </c>
       <c r="F2" s="67" t="s">
@@ -6751,126 +10717,126 @@
         <v>817</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="78">
+    <row r="3" spans="1:7" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="92">
         <v>1</v>
       </c>
-      <c r="B3" s="100" t="s">
-        <v>439</v>
-      </c>
-      <c r="C3" s="101"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="80" t="s">
+      <c r="B3" s="110" t="s">
+        <v>928</v>
+      </c>
+      <c r="C3" s="111"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="94" t="s">
         <v>829</v>
       </c>
-      <c r="F3" s="78" t="s">
+      <c r="F3" s="92" t="s">
         <v>46</v>
       </c>
       <c r="G3" s="70">
         <f>B11</f>
-        <v>4716.6000000000004</v>
+        <v>4683.1000000000004</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="103"/>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
     </row>
     <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="92" t="s">
         <v>831</v>
       </c>
-      <c r="B5" s="78" t="s">
+      <c r="B5" s="92" t="s">
         <v>821</v>
       </c>
-      <c r="C5" s="104"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="105"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="78">
+      <c r="A6" s="92">
         <v>1</v>
       </c>
       <c r="B6" s="70">
-        <v>905.8</v>
-      </c>
-      <c r="C6" s="104"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="105"/>
+        <v>897.3</v>
+      </c>
+      <c r="C6" s="114"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="78">
+      <c r="A7" s="92">
         <v>2</v>
       </c>
       <c r="B7" s="70">
-        <v>911.4</v>
-      </c>
-      <c r="C7" s="104"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
+        <v>903.4</v>
+      </c>
+      <c r="C7" s="114"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="115"/>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="78">
+      <c r="A8" s="92">
         <v>3</v>
       </c>
       <c r="B8" s="70">
-        <v>905.40000000000009</v>
-      </c>
-      <c r="C8" s="104"/>
-      <c r="D8" s="105"/>
-      <c r="E8" s="105"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="105"/>
+        <v>902.4</v>
+      </c>
+      <c r="C8" s="114"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="115"/>
     </row>
     <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="78">
+      <c r="A9" s="92">
         <v>4</v>
       </c>
       <c r="B9" s="70">
-        <v>1005.4000000000001</v>
-      </c>
-      <c r="C9" s="104"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-      <c r="G9" s="105"/>
+        <v>1001.4</v>
+      </c>
+      <c r="C9" s="114"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="78">
+      <c r="A10" s="92">
         <v>5</v>
       </c>
       <c r="B10" s="70">
-        <v>988.60000000000014</v>
-      </c>
-      <c r="C10" s="104"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="105"/>
+        <v>978.6</v>
+      </c>
+      <c r="C10" s="114"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="115"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="81" t="s">
+      <c r="A11" s="95" t="s">
         <v>828</v>
       </c>
       <c r="B11" s="70">
         <f>SUM(B6:B10)</f>
-        <v>4716.6000000000004</v>
-      </c>
-      <c r="C11" s="104"/>
-      <c r="D11" s="105"/>
-      <c r="E11" s="105"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="105"/>
+        <v>4683.1000000000004</v>
+      </c>
+      <c r="C11" s="114"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="115"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="115"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6880,1470 +10846,6 @@
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="C5:G11"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Лист1">
-    <tabColor rgb="FF00B0F0"/>
-  </sheetPr>
-  <dimension ref="A1:L90"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="88"/>
-    <col min="2" max="4" width="13.88671875" style="77" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="77"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" s="87" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="86" t="s">
-        <v>894</v>
-      </c>
-      <c r="B1" s="87" t="s">
-        <v>895</v>
-      </c>
-      <c r="C1" s="87" t="s">
-        <v>896</v>
-      </c>
-      <c r="D1" s="87" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="88" t="s">
-        <v>854</v>
-      </c>
-      <c r="B2" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C2" s="77">
-        <v>54.2</v>
-      </c>
-      <c r="D2" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="88" t="s">
-        <v>855</v>
-      </c>
-      <c r="B3" s="77">
-        <v>45.03</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D3" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="G3" s="77">
-        <v>0</v>
-      </c>
-      <c r="H3" s="77">
-        <v>1</v>
-      </c>
-      <c r="I3" s="77">
-        <v>2</v>
-      </c>
-      <c r="J3" s="77">
-        <v>3</v>
-      </c>
-      <c r="K3" s="77">
-        <v>4</v>
-      </c>
-      <c r="L3" s="77">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="88" t="s">
-        <v>856</v>
-      </c>
-      <c r="B4" s="77">
-        <v>278.32</v>
-      </c>
-      <c r="C4" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D4" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="G4" s="77">
-        <v>1749</v>
-      </c>
-      <c r="H4" s="77">
-        <v>11.7</v>
-      </c>
-      <c r="I4" s="77">
-        <v>86.7</v>
-      </c>
-      <c r="J4" s="77">
-        <v>170.3</v>
-      </c>
-      <c r="K4" s="77">
-        <v>174.1</v>
-      </c>
-      <c r="L4" s="77">
-        <v>728.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="88" t="s">
-        <v>857</v>
-      </c>
-      <c r="B5" s="77">
-        <v>29.72</v>
-      </c>
-      <c r="C5" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D5" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="G5" s="77">
-        <v>254.2</v>
-      </c>
-      <c r="H5" s="77">
-        <v>81.900000000000006</v>
-      </c>
-      <c r="I5" s="77">
-        <v>481.4</v>
-      </c>
-      <c r="J5" s="77">
-        <v>397.6</v>
-      </c>
-      <c r="K5" s="77">
-        <v>407.6</v>
-      </c>
-      <c r="L5" s="77">
-        <v>198.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="88" t="s">
-        <v>839</v>
-      </c>
-      <c r="B6" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C6" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D6" s="77">
-        <v>144.29</v>
-      </c>
-      <c r="G6" s="77">
-        <v>910.3</v>
-      </c>
-      <c r="H6" s="77">
-        <v>279.7</v>
-      </c>
-      <c r="I6" s="77">
-        <v>286</v>
-      </c>
-      <c r="J6" s="77">
-        <v>277</v>
-      </c>
-      <c r="K6" s="77">
-        <v>366.9</v>
-      </c>
-      <c r="L6" s="77">
-        <v>48.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="88" t="s">
-        <v>858</v>
-      </c>
-      <c r="B7" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C7" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D7" s="77">
-        <v>144.29</v>
-      </c>
-      <c r="G7" s="77">
-        <v>11.2</v>
-      </c>
-      <c r="H7" s="77">
-        <v>456</v>
-      </c>
-      <c r="I7" s="77">
-        <v>57.3</v>
-      </c>
-      <c r="J7" s="77">
-        <v>60.5</v>
-      </c>
-      <c r="K7" s="77">
-        <v>43.2</v>
-      </c>
-      <c r="L7" s="77">
-        <v>13.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="88" t="s">
-        <v>859</v>
-      </c>
-      <c r="B8" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C8" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D8" s="77">
-        <v>144.29</v>
-      </c>
-      <c r="H8" s="77">
-        <v>76.5</v>
-      </c>
-      <c r="K8" s="77">
-        <v>13.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="88" t="s">
-        <v>860</v>
-      </c>
-      <c r="B9" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C9" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D9" s="77">
-        <v>144.29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88" t="s">
-        <v>861</v>
-      </c>
-      <c r="B10" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C10" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D10" s="77">
-        <v>253.19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88" t="s">
-        <v>862</v>
-      </c>
-      <c r="B11" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C11" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D11" s="77">
-        <v>144.29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="88" t="s">
-        <v>863</v>
-      </c>
-      <c r="B12" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C12" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D12" s="77">
-        <v>253.19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="88" t="s">
-        <v>864</v>
-      </c>
-      <c r="B13" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C13" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D13" s="77">
-        <v>144.29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88" t="s">
-        <v>865</v>
-      </c>
-      <c r="B14" s="77">
-        <v>157.04</v>
-      </c>
-      <c r="C14" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D14" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88" t="s">
-        <v>840</v>
-      </c>
-      <c r="B15" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C15" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D15" s="77">
-        <v>33.53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="88" t="s">
-        <v>866</v>
-      </c>
-      <c r="B16" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C16" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D16" s="77">
-        <v>17.09</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="88" t="s">
-        <v>867</v>
-      </c>
-      <c r="B17" s="77">
-        <v>31.06</v>
-      </c>
-      <c r="C17" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D17" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="88" t="s">
-        <v>868</v>
-      </c>
-      <c r="B18" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C18" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D18" s="77">
-        <v>12.67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="88" t="s">
-        <v>869</v>
-      </c>
-      <c r="B19" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C19" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D19" s="77">
-        <v>144.29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="88" t="s">
-        <v>870</v>
-      </c>
-      <c r="B20" s="77">
-        <v>157.04</v>
-      </c>
-      <c r="C20" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D20" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="88" t="s">
-        <v>841</v>
-      </c>
-      <c r="B21" s="77">
-        <v>157.04</v>
-      </c>
-      <c r="C21" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D21" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="88" t="s">
-        <v>842</v>
-      </c>
-      <c r="B22" s="77">
-        <v>157.04</v>
-      </c>
-      <c r="C22" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D22" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="88" t="s">
-        <v>843</v>
-      </c>
-      <c r="B23" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C23" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D23" s="77">
-        <v>144.29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="88" t="s">
-        <v>871</v>
-      </c>
-      <c r="B24" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C24" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D24" s="77">
-        <v>144.29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="88" t="s">
-        <v>872</v>
-      </c>
-      <c r="B25" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C25" s="77">
-        <v>54.2</v>
-      </c>
-      <c r="D25" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="88" t="s">
-        <v>873</v>
-      </c>
-      <c r="B26" s="77">
-        <v>32.130000000000003</v>
-      </c>
-      <c r="C26" s="77">
-        <v>17.690000000000001</v>
-      </c>
-      <c r="D26" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="88" t="s">
-        <v>874</v>
-      </c>
-      <c r="B27" s="77">
-        <v>157.04</v>
-      </c>
-      <c r="C27" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D27" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="88" t="s">
-        <v>844</v>
-      </c>
-      <c r="B28" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C28" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D28" s="77">
-        <v>144.29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="88" t="s">
-        <v>875</v>
-      </c>
-      <c r="B29" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C29" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D29" s="77">
-        <v>144.29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="88" t="s">
-        <v>876</v>
-      </c>
-      <c r="B30" s="77">
-        <v>157.04</v>
-      </c>
-      <c r="C30" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D30" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="88" t="s">
-        <v>845</v>
-      </c>
-      <c r="B31" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C31" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D31" s="77">
-        <v>253.19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="88" t="s">
-        <v>877</v>
-      </c>
-      <c r="B32" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C32" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D32" s="77">
-        <v>109.3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="88" t="s">
-        <v>878</v>
-      </c>
-      <c r="B33" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C33" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D33" s="77">
-        <v>33.53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="88" t="s">
-        <v>879</v>
-      </c>
-      <c r="B34" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C34" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D34" s="77">
-        <v>9.6300000000000008</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="88" t="s">
-        <v>880</v>
-      </c>
-      <c r="B35" s="77">
-        <v>278.32</v>
-      </c>
-      <c r="C35" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D35" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="88" t="s">
-        <v>881</v>
-      </c>
-      <c r="B36" s="77">
-        <v>157.04</v>
-      </c>
-      <c r="C36" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D36" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="88" t="s">
-        <v>846</v>
-      </c>
-      <c r="B37" s="77">
-        <v>24.96</v>
-      </c>
-      <c r="C37" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D37" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="88" t="s">
-        <v>882</v>
-      </c>
-      <c r="B38" s="77">
-        <v>157.04</v>
-      </c>
-      <c r="C38" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D38" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="88" t="s">
-        <v>847</v>
-      </c>
-      <c r="B39" s="77">
-        <v>157.04</v>
-      </c>
-      <c r="C39" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D39" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="88" t="s">
-        <v>848</v>
-      </c>
-      <c r="B40" s="77">
-        <v>157.04</v>
-      </c>
-      <c r="C40" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D40" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="88" t="s">
-        <v>849</v>
-      </c>
-      <c r="B41" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C41" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D41" s="77">
-        <v>253.19</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="88" t="s">
-        <v>883</v>
-      </c>
-      <c r="B42" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C42" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D42" s="77">
-        <v>109.3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="88" t="s">
-        <v>884</v>
-      </c>
-      <c r="B43" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C43" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D43" s="77">
-        <v>33.53</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="88" t="s">
-        <v>885</v>
-      </c>
-      <c r="B44" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C44" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D44" s="77">
-        <v>9.6300000000000008</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="88" t="s">
-        <v>886</v>
-      </c>
-      <c r="B45" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C45" s="77">
-        <v>110.62</v>
-      </c>
-      <c r="D45" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="88" t="s">
-        <v>887</v>
-      </c>
-      <c r="B46" s="77">
-        <v>45.03</v>
-      </c>
-      <c r="C46" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D46" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="88" t="s">
-        <v>888</v>
-      </c>
-      <c r="B47" s="77">
-        <v>157.04</v>
-      </c>
-      <c r="C47" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D47" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="88" t="s">
-        <v>850</v>
-      </c>
-      <c r="B48" s="77">
-        <v>5.44</v>
-      </c>
-      <c r="C48" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D48" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="88" t="s">
-        <v>889</v>
-      </c>
-      <c r="B49" s="77">
-        <v>157.04</v>
-      </c>
-      <c r="C49" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D49" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="88" t="s">
-        <v>851</v>
-      </c>
-      <c r="B50" s="77">
-        <v>31.06</v>
-      </c>
-      <c r="C50" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D50" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="88" t="s">
-        <v>852</v>
-      </c>
-      <c r="B51" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C51" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D51" s="77">
-        <v>109.3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="88" t="s">
-        <v>890</v>
-      </c>
-      <c r="B52" s="77">
-        <v>14.17</v>
-      </c>
-      <c r="C52" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D52" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="88" t="s">
-        <v>853</v>
-      </c>
-      <c r="B53" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C53" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D53" s="77">
-        <v>253.19</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="88" t="s">
-        <v>891</v>
-      </c>
-      <c r="B54" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C54" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D54" s="77">
-        <v>253.19</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="88" t="s">
-        <v>892</v>
-      </c>
-      <c r="B55" s="77">
-        <v>31.06</v>
-      </c>
-      <c r="C55" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D55" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="88" t="s">
-        <v>893</v>
-      </c>
-      <c r="B56" s="77">
-        <v>44.74</v>
-      </c>
-      <c r="C56" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D56" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="88" t="s">
-        <v>898</v>
-      </c>
-      <c r="B60" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C60" s="77">
-        <v>77.23</v>
-      </c>
-      <c r="D60" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="88" t="s">
-        <v>899</v>
-      </c>
-      <c r="B61" s="77">
-        <v>24.2</v>
-      </c>
-      <c r="C61" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D61" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="88" t="s">
-        <v>900</v>
-      </c>
-      <c r="B62" s="77">
-        <v>73.42</v>
-      </c>
-      <c r="C62" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D62" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="88" t="s">
-        <v>901</v>
-      </c>
-      <c r="B63" s="77">
-        <v>91.72</v>
-      </c>
-      <c r="C63" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D63" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="88" t="s">
-        <v>836</v>
-      </c>
-      <c r="B64" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C64" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D64" s="77">
-        <v>104.72</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="88" t="s">
-        <v>837</v>
-      </c>
-      <c r="B65" s="77">
-        <v>234.98</v>
-      </c>
-      <c r="C65" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D65" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="88" t="s">
-        <v>902</v>
-      </c>
-      <c r="B66" s="77">
-        <v>91.72</v>
-      </c>
-      <c r="C66" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D66" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="88" t="s">
-        <v>903</v>
-      </c>
-      <c r="B67" s="77">
-        <v>91.72</v>
-      </c>
-      <c r="C67" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D67" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="88" t="s">
-        <v>904</v>
-      </c>
-      <c r="B68" s="77">
-        <v>56.51</v>
-      </c>
-      <c r="C68" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D68" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="88" t="s">
-        <v>838</v>
-      </c>
-      <c r="B69" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C69" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D69" s="77">
-        <v>104.72</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="88" t="s">
-        <v>905</v>
-      </c>
-      <c r="B70" s="77">
-        <v>91.72</v>
-      </c>
-      <c r="C70" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D70" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="88" t="s">
-        <v>906</v>
-      </c>
-      <c r="B71" s="77">
-        <v>7.81</v>
-      </c>
-      <c r="C71" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D71" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="88" t="s">
-        <v>907</v>
-      </c>
-      <c r="B72" s="77">
-        <v>91.72</v>
-      </c>
-      <c r="C72" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D72" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="88" t="s">
-        <v>908</v>
-      </c>
-      <c r="B73" s="77">
-        <v>91.72</v>
-      </c>
-      <c r="C73" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D73" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="88" t="s">
-        <v>909</v>
-      </c>
-      <c r="B74" s="77">
-        <v>48.37</v>
-      </c>
-      <c r="C74" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D74" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="88" t="s">
-        <v>910</v>
-      </c>
-      <c r="B75" s="77">
-        <v>29.8</v>
-      </c>
-      <c r="C75" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D75" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="88" t="s">
-        <v>911</v>
-      </c>
-      <c r="B76" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C76" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D76" s="77">
-        <v>31.04</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="88" t="s">
-        <v>912</v>
-      </c>
-      <c r="B77" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C77" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D77" s="77">
-        <v>104.72</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="88" t="s">
-        <v>913</v>
-      </c>
-      <c r="B78" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C78" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D78" s="77">
-        <v>234.98</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="88" t="s">
-        <v>914</v>
-      </c>
-      <c r="B79" s="77">
-        <v>18.579999999999998</v>
-      </c>
-      <c r="C79" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D79" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="88" t="s">
-        <v>915</v>
-      </c>
-      <c r="B80" s="77">
-        <v>56.51</v>
-      </c>
-      <c r="C80" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D80" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="88" t="s">
-        <v>916</v>
-      </c>
-      <c r="B81" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C81" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D81" s="77">
-        <v>234.98</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="88" t="s">
-        <v>917</v>
-      </c>
-      <c r="B82" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C82" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D82" s="77">
-        <v>234.98</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="88" t="s">
-        <v>918</v>
-      </c>
-      <c r="B83" s="77">
-        <v>33.92</v>
-      </c>
-      <c r="C83" s="77">
-        <v>17.690000000000001</v>
-      </c>
-      <c r="D83" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="88" t="s">
-        <v>919</v>
-      </c>
-      <c r="B84" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C84" s="77">
-        <v>27.88</v>
-      </c>
-      <c r="D84" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="88" t="s">
-        <v>920</v>
-      </c>
-      <c r="B85" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C85" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D85" s="77">
-        <v>234.98</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="88" t="s">
-        <v>921</v>
-      </c>
-      <c r="B86" s="77">
-        <v>56.51</v>
-      </c>
-      <c r="C86" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D86" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="88" t="s">
-        <v>922</v>
-      </c>
-      <c r="B87" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="C87" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D87" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="88" t="s">
-        <v>923</v>
-      </c>
-      <c r="B88" s="77">
-        <v>203.07</v>
-      </c>
-      <c r="C88" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D88" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="88" t="s">
-        <v>924</v>
-      </c>
-      <c r="B89" s="77">
-        <v>203.07</v>
-      </c>
-      <c r="C89" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D89" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="88" t="s">
-        <v>925</v>
-      </c>
-      <c r="B90" s="77">
-        <v>73.42</v>
-      </c>
-      <c r="C90" s="77" t="s">
-        <v>835</v>
-      </c>
-      <c r="D90" s="77" t="s">
-        <v>835</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Лист2">
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="43.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="56.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
-    <col min="6" max="8" width="16.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="56" t="s">
-        <v>757</v>
-      </c>
-      <c r="D1" s="60" t="s">
-        <v>758</v>
-      </c>
-      <c r="E1" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="60" t="s">
-        <v>813</v>
-      </c>
-      <c r="H1" s="60" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" s="42">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="59">
-        <f t="shared" ref="F2:F4" si="0">SUM(G2:H2)</f>
-        <v>247.184</v>
-      </c>
-      <c r="G2" s="8">
-        <v>186.2</v>
-      </c>
-      <c r="H2" s="8">
-        <v>60.984000000000009</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="42">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="59">
-        <f>SUM(G3:H3)</f>
-        <v>49.534000000000006</v>
-      </c>
-      <c r="G3" s="8">
-        <v>18.3</v>
-      </c>
-      <c r="H3" s="8">
-        <v>31.234000000000002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="42">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="59">
-        <f t="shared" si="0"/>
-        <v>28.867000000000004</v>
-      </c>
-      <c r="G4" s="8">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="H4" s="8">
-        <v>10.767000000000001</v>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8364,25 +10866,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="106" t="s">
         <v>814</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="65" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="116" t="s">
         <v>816</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="118"/>
       <c r="E2" s="66" t="s">
         <v>758</v>
       </c>
@@ -8397,11 +10899,11 @@
       <c r="A3" s="68">
         <v>1</v>
       </c>
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="119" t="s">
         <v>516</v>
       </c>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="121"/>
       <c r="E3" s="69" t="s">
         <v>830</v>
       </c>
@@ -8414,24 +10916,24 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="103"/>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="112" t="s">
+      <c r="A5" s="122" t="s">
         <v>818</v>
       </c>
-      <c r="B5" s="112"/>
-      <c r="C5" s="112"/>
-      <c r="D5" s="112"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="105"/>
+      <c r="B5" s="122"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="68" t="s">
@@ -8446,9 +10948,9 @@
       <c r="D6" s="68" t="s">
         <v>822</v>
       </c>
-      <c r="E6" s="105"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="105"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="68">
@@ -8464,9 +10966,9 @@
       <c r="D7" s="71">
         <v>228</v>
       </c>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="115"/>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="68">
@@ -8482,9 +10984,9 @@
       <c r="D8" s="71">
         <v>247.1</v>
       </c>
-      <c r="E8" s="105"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="105"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="115"/>
     </row>
     <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="68">
@@ -8500,9 +11002,9 @@
       <c r="D9" s="71">
         <v>243.6</v>
       </c>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-      <c r="G9" s="105"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="68">
@@ -8518,9 +11020,9 @@
       <c r="D10" s="71">
         <v>243.6</v>
       </c>
-      <c r="E10" s="105"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="105"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="115"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="68">
@@ -8536,15 +11038,15 @@
       <c r="D11" s="71">
         <v>117.4</v>
       </c>
-      <c r="E11" s="105"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="105"/>
+      <c r="E11" s="115"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="115"/>
     </row>
     <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="113" t="s">
+      <c r="A12" s="123" t="s">
         <v>828</v>
       </c>
-      <c r="B12" s="114"/>
+      <c r="B12" s="124"/>
       <c r="C12" s="73">
         <f>SUM(C7:C11)</f>
         <v>4102.8599999999997</v>
@@ -8552,9 +11054,9 @@
       <c r="D12" s="73">
         <v>1200</v>
       </c>
-      <c r="E12" s="105"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
+      <c r="E12" s="115"/>
+      <c r="F12" s="115"/>
+      <c r="G12" s="115"/>
     </row>
     <row r="17" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I17" t="s">
@@ -8741,61 +11243,61 @@
       <c r="O1" s="19"/>
     </row>
     <row r="2" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="125" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="115"/>
-      <c r="M2" s="115"/>
-      <c r="N2" s="115"/>
-      <c r="O2" s="115"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="125"/>
     </row>
     <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="116" t="s">
+      <c r="A3" s="126" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="116"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
-      <c r="H3" s="116"/>
-      <c r="I3" s="116"/>
-      <c r="J3" s="116"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="116"/>
-      <c r="M3" s="116"/>
-      <c r="N3" s="116"/>
-      <c r="O3" s="116"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="126"/>
+      <c r="K3" s="126"/>
+      <c r="L3" s="126"/>
+      <c r="M3" s="126"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="126"/>
     </row>
     <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="115" t="s">
+      <c r="A4" s="125" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="115"/>
-      <c r="C4" s="115"/>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="115"/>
-      <c r="L4" s="115"/>
-      <c r="M4" s="115"/>
-      <c r="N4" s="115"/>
-      <c r="O4" s="115"/>
+      <c r="B4" s="125"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="125"/>
+      <c r="M4" s="125"/>
+      <c r="N4" s="125"/>
+      <c r="O4" s="125"/>
     </row>
     <row r="5" spans="1:18" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
@@ -8848,17 +11350,17 @@
       <c r="R5" s="13"/>
     </row>
     <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="117" t="s">
+      <c r="A6" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="118"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="118"/>
-      <c r="F6" s="118"/>
-      <c r="G6" s="118"/>
-      <c r="H6" s="118"/>
-      <c r="I6" s="118"/>
+      <c r="B6" s="128"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="128"/>
+      <c r="E6" s="128"/>
+      <c r="F6" s="128"/>
+      <c r="G6" s="128"/>
+      <c r="H6" s="128"/>
+      <c r="I6" s="128"/>
       <c r="J6" s="21"/>
       <c r="K6" s="21"/>
       <c r="L6" s="21"/>
@@ -8874,15 +11376,15 @@
       <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="119" t="s">
+      <c r="C7" s="129" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="120"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="120"/>
-      <c r="G7" s="120"/>
-      <c r="H7" s="120"/>
-      <c r="I7" s="120"/>
+      <c r="D7" s="130"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="130"/>
+      <c r="G7" s="130"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="130"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
@@ -8898,15 +11400,15 @@
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="119" t="s">
+      <c r="C8" s="129" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="120"/>
-      <c r="I8" s="120"/>
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="130"/>
+      <c r="G8" s="130"/>
+      <c r="H8" s="130"/>
+      <c r="I8" s="130"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
@@ -8922,15 +11424,15 @@
       <c r="B9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="119" t="s">
+      <c r="C9" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="120"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="120"/>
-      <c r="H9" s="120"/>
-      <c r="I9" s="120"/>
+      <c r="D9" s="130"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="130"/>
+      <c r="G9" s="130"/>
+      <c r="H9" s="130"/>
+      <c r="I9" s="130"/>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
@@ -8946,15 +11448,15 @@
       <c r="B10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="119" t="s">
+      <c r="C10" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="120"/>
-      <c r="E10" s="120"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="120"/>
-      <c r="H10" s="120"/>
-      <c r="I10" s="120"/>
+      <c r="D10" s="130"/>
+      <c r="E10" s="130"/>
+      <c r="F10" s="130"/>
+      <c r="G10" s="130"/>
+      <c r="H10" s="130"/>
+      <c r="I10" s="130"/>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
@@ -8970,15 +11472,15 @@
       <c r="B11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="119" t="s">
+      <c r="C11" s="129" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="120"/>
-      <c r="E11" s="120"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="120"/>
-      <c r="H11" s="120"/>
-      <c r="I11" s="120"/>
+      <c r="D11" s="130"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="130"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="130"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
@@ -8994,15 +11496,15 @@
       <c r="B12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="119" t="s">
+      <c r="C12" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="120"/>
-      <c r="E12" s="120"/>
-      <c r="F12" s="120"/>
-      <c r="G12" s="120"/>
-      <c r="H12" s="120"/>
-      <c r="I12" s="120"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="130"/>
+      <c r="G12" s="130"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="130"/>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
@@ -12040,15 +14542,15 @@
       <c r="B108" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C108" s="119" t="s">
+      <c r="C108" s="129" t="s">
         <v>166</v>
       </c>
-      <c r="D108" s="120"/>
-      <c r="E108" s="120"/>
-      <c r="F108" s="120"/>
-      <c r="G108" s="120"/>
-      <c r="H108" s="120"/>
-      <c r="I108" s="120"/>
+      <c r="D108" s="130"/>
+      <c r="E108" s="130"/>
+      <c r="F108" s="130"/>
+      <c r="G108" s="130"/>
+      <c r="H108" s="130"/>
+      <c r="I108" s="130"/>
       <c r="J108" s="9"/>
       <c r="K108" s="9"/>
       <c r="L108" s="9"/>
@@ -12064,15 +14566,15 @@
       <c r="B109" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C109" s="119" t="s">
+      <c r="C109" s="129" t="s">
         <v>169</v>
       </c>
-      <c r="D109" s="120"/>
-      <c r="E109" s="120"/>
-      <c r="F109" s="120"/>
-      <c r="G109" s="120"/>
-      <c r="H109" s="120"/>
-      <c r="I109" s="120"/>
+      <c r="D109" s="130"/>
+      <c r="E109" s="130"/>
+      <c r="F109" s="130"/>
+      <c r="G109" s="130"/>
+      <c r="H109" s="130"/>
+      <c r="I109" s="130"/>
       <c r="J109" s="9"/>
       <c r="K109" s="9"/>
       <c r="L109" s="9"/>
@@ -12088,15 +14590,15 @@
       <c r="B110" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C110" s="119" t="s">
+      <c r="C110" s="129" t="s">
         <v>172</v>
       </c>
-      <c r="D110" s="120"/>
-      <c r="E110" s="120"/>
-      <c r="F110" s="120"/>
-      <c r="G110" s="120"/>
-      <c r="H110" s="120"/>
-      <c r="I110" s="120"/>
+      <c r="D110" s="130"/>
+      <c r="E110" s="130"/>
+      <c r="F110" s="130"/>
+      <c r="G110" s="130"/>
+      <c r="H110" s="130"/>
+      <c r="I110" s="130"/>
       <c r="J110" s="9"/>
       <c r="K110" s="9"/>
       <c r="L110" s="9"/>
@@ -12112,15 +14614,15 @@
       <c r="B111" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C111" s="119" t="s">
+      <c r="C111" s="129" t="s">
         <v>175</v>
       </c>
-      <c r="D111" s="120"/>
-      <c r="E111" s="120"/>
-      <c r="F111" s="120"/>
-      <c r="G111" s="120"/>
-      <c r="H111" s="120"/>
-      <c r="I111" s="120"/>
+      <c r="D111" s="130"/>
+      <c r="E111" s="130"/>
+      <c r="F111" s="130"/>
+      <c r="G111" s="130"/>
+      <c r="H111" s="130"/>
+      <c r="I111" s="130"/>
       <c r="J111" s="9"/>
       <c r="K111" s="9"/>
       <c r="L111" s="9"/>
@@ -12136,15 +14638,15 @@
       <c r="B112" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C112" s="119" t="s">
+      <c r="C112" s="129" t="s">
         <v>178</v>
       </c>
-      <c r="D112" s="120"/>
-      <c r="E112" s="120"/>
-      <c r="F112" s="120"/>
-      <c r="G112" s="120"/>
-      <c r="H112" s="120"/>
-      <c r="I112" s="120"/>
+      <c r="D112" s="130"/>
+      <c r="E112" s="130"/>
+      <c r="F112" s="130"/>
+      <c r="G112" s="130"/>
+      <c r="H112" s="130"/>
+      <c r="I112" s="130"/>
       <c r="J112" s="9"/>
       <c r="K112" s="9"/>
       <c r="L112" s="9"/>
@@ -12871,15 +15373,15 @@
       <c r="B135" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C135" s="119" t="s">
+      <c r="C135" s="129" t="s">
         <v>219</v>
       </c>
-      <c r="D135" s="120"/>
-      <c r="E135" s="120"/>
-      <c r="F135" s="120"/>
-      <c r="G135" s="120"/>
-      <c r="H135" s="120"/>
-      <c r="I135" s="120"/>
+      <c r="D135" s="130"/>
+      <c r="E135" s="130"/>
+      <c r="F135" s="130"/>
+      <c r="G135" s="130"/>
+      <c r="H135" s="130"/>
+      <c r="I135" s="130"/>
       <c r="J135" s="9"/>
       <c r="K135" s="9"/>
       <c r="L135" s="9"/>
@@ -14406,15 +16908,15 @@
       <c r="B180" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C180" s="119" t="s">
+      <c r="C180" s="129" t="s">
         <v>285</v>
       </c>
-      <c r="D180" s="120"/>
-      <c r="E180" s="120"/>
-      <c r="F180" s="120"/>
-      <c r="G180" s="120"/>
-      <c r="H180" s="120"/>
-      <c r="I180" s="120"/>
+      <c r="D180" s="130"/>
+      <c r="E180" s="130"/>
+      <c r="F180" s="130"/>
+      <c r="G180" s="130"/>
+      <c r="H180" s="130"/>
+      <c r="I180" s="130"/>
       <c r="J180" s="9"/>
       <c r="K180" s="9"/>
       <c r="L180" s="9"/>
@@ -17767,15 +20269,15 @@
       <c r="B285" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C285" s="119" t="s">
+      <c r="C285" s="129" t="s">
         <v>433</v>
       </c>
-      <c r="D285" s="120"/>
-      <c r="E285" s="120"/>
-      <c r="F285" s="120"/>
-      <c r="G285" s="120"/>
-      <c r="H285" s="120"/>
-      <c r="I285" s="120"/>
+      <c r="D285" s="130"/>
+      <c r="E285" s="130"/>
+      <c r="F285" s="130"/>
+      <c r="G285" s="130"/>
+      <c r="H285" s="130"/>
+      <c r="I285" s="130"/>
       <c r="J285" s="9"/>
       <c r="K285" s="9"/>
       <c r="L285" s="9"/>
@@ -17791,15 +20293,15 @@
       <c r="B286" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C286" s="119" t="s">
+      <c r="C286" s="129" t="s">
         <v>436</v>
       </c>
-      <c r="D286" s="120"/>
-      <c r="E286" s="120"/>
-      <c r="F286" s="120"/>
-      <c r="G286" s="120"/>
-      <c r="H286" s="120"/>
-      <c r="I286" s="120"/>
+      <c r="D286" s="130"/>
+      <c r="E286" s="130"/>
+      <c r="F286" s="130"/>
+      <c r="G286" s="130"/>
+      <c r="H286" s="130"/>
+      <c r="I286" s="130"/>
       <c r="J286" s="9"/>
       <c r="K286" s="9"/>
       <c r="L286" s="9"/>
@@ -18136,15 +20638,15 @@
       <c r="B297" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="C297" s="119" t="s">
+      <c r="C297" s="129" t="s">
         <v>455</v>
       </c>
-      <c r="D297" s="120"/>
-      <c r="E297" s="120"/>
-      <c r="F297" s="120"/>
-      <c r="G297" s="120"/>
-      <c r="H297" s="120"/>
-      <c r="I297" s="120"/>
+      <c r="D297" s="130"/>
+      <c r="E297" s="130"/>
+      <c r="F297" s="130"/>
+      <c r="G297" s="130"/>
+      <c r="H297" s="130"/>
+      <c r="I297" s="130"/>
       <c r="J297" s="9"/>
       <c r="K297" s="9"/>
       <c r="L297" s="9"/>
@@ -19014,15 +21516,15 @@
       <c r="B324" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="C324" s="119" t="s">
+      <c r="C324" s="129" t="s">
         <v>498</v>
       </c>
-      <c r="D324" s="120"/>
-      <c r="E324" s="120"/>
-      <c r="F324" s="120"/>
-      <c r="G324" s="120"/>
-      <c r="H324" s="120"/>
-      <c r="I324" s="120"/>
+      <c r="D324" s="130"/>
+      <c r="E324" s="130"/>
+      <c r="F324" s="130"/>
+      <c r="G324" s="130"/>
+      <c r="H324" s="130"/>
+      <c r="I324" s="130"/>
       <c r="J324" s="9"/>
       <c r="K324" s="9"/>
       <c r="L324" s="9"/>
@@ -19038,15 +21540,15 @@
       <c r="B325" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="C325" s="119" t="s">
+      <c r="C325" s="129" t="s">
         <v>501</v>
       </c>
-      <c r="D325" s="120"/>
-      <c r="E325" s="120"/>
-      <c r="F325" s="120"/>
-      <c r="G325" s="120"/>
-      <c r="H325" s="120"/>
-      <c r="I325" s="120"/>
+      <c r="D325" s="130"/>
+      <c r="E325" s="130"/>
+      <c r="F325" s="130"/>
+      <c r="G325" s="130"/>
+      <c r="H325" s="130"/>
+      <c r="I325" s="130"/>
       <c r="J325" s="9"/>
       <c r="K325" s="9"/>
       <c r="L325" s="9"/>
@@ -19576,15 +22078,15 @@
       <c r="B342" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="C342" s="119" t="s">
+      <c r="C342" s="129" t="s">
         <v>525</v>
       </c>
-      <c r="D342" s="120"/>
-      <c r="E342" s="120"/>
-      <c r="F342" s="120"/>
-      <c r="G342" s="120"/>
-      <c r="H342" s="120"/>
-      <c r="I342" s="120"/>
+      <c r="D342" s="130"/>
+      <c r="E342" s="130"/>
+      <c r="F342" s="130"/>
+      <c r="G342" s="130"/>
+      <c r="H342" s="130"/>
+      <c r="I342" s="130"/>
       <c r="J342" s="9"/>
       <c r="K342" s="9"/>
       <c r="L342" s="9"/>
@@ -20396,15 +22898,15 @@
       <c r="B367" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="C367" s="119" t="s">
+      <c r="C367" s="129" t="s">
         <v>559</v>
       </c>
-      <c r="D367" s="120"/>
-      <c r="E367" s="120"/>
-      <c r="F367" s="120"/>
-      <c r="G367" s="120"/>
-      <c r="H367" s="120"/>
-      <c r="I367" s="120"/>
+      <c r="D367" s="130"/>
+      <c r="E367" s="130"/>
+      <c r="F367" s="130"/>
+      <c r="G367" s="130"/>
+      <c r="H367" s="130"/>
+      <c r="I367" s="130"/>
       <c r="J367" s="9"/>
       <c r="K367" s="9"/>
       <c r="L367" s="9"/>
@@ -22908,15 +25410,15 @@
       <c r="B447" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="C447" s="119" t="s">
+      <c r="C447" s="129" t="s">
         <v>664</v>
       </c>
-      <c r="D447" s="120"/>
-      <c r="E447" s="120"/>
-      <c r="F447" s="120"/>
-      <c r="G447" s="120"/>
-      <c r="H447" s="120"/>
-      <c r="I447" s="120"/>
+      <c r="D447" s="130"/>
+      <c r="E447" s="130"/>
+      <c r="F447" s="130"/>
+      <c r="G447" s="130"/>
+      <c r="H447" s="130"/>
+      <c r="I447" s="130"/>
       <c r="J447" s="9"/>
       <c r="K447" s="9"/>
       <c r="L447" s="9"/>
@@ -23004,17 +25506,17 @@
       <c r="P449" s="9"/>
     </row>
     <row r="450" spans="1:18" ht="64.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A450" s="117" t="s">
+      <c r="A450" s="127" t="s">
         <v>671</v>
       </c>
-      <c r="B450" s="118"/>
-      <c r="C450" s="118"/>
-      <c r="D450" s="118"/>
-      <c r="E450" s="118"/>
-      <c r="F450" s="118"/>
-      <c r="G450" s="118"/>
-      <c r="H450" s="118"/>
-      <c r="I450" s="118"/>
+      <c r="B450" s="128"/>
+      <c r="C450" s="128"/>
+      <c r="D450" s="128"/>
+      <c r="E450" s="128"/>
+      <c r="F450" s="128"/>
+      <c r="G450" s="128"/>
+      <c r="H450" s="128"/>
+      <c r="I450" s="128"/>
       <c r="J450" s="26"/>
       <c r="K450" s="26"/>
       <c r="L450" s="26"/>
@@ -23030,15 +25532,15 @@
       <c r="B451" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C451" s="119" t="s">
+      <c r="C451" s="129" t="s">
         <v>25</v>
       </c>
-      <c r="D451" s="120"/>
-      <c r="E451" s="120"/>
-      <c r="F451" s="120"/>
-      <c r="G451" s="120"/>
-      <c r="H451" s="120"/>
-      <c r="I451" s="120"/>
+      <c r="D451" s="130"/>
+      <c r="E451" s="130"/>
+      <c r="F451" s="130"/>
+      <c r="G451" s="130"/>
+      <c r="H451" s="130"/>
+      <c r="I451" s="130"/>
       <c r="J451" s="9"/>
       <c r="K451" s="9"/>
       <c r="L451" s="9"/>
@@ -23054,15 +25556,15 @@
       <c r="B452" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C452" s="119" t="s">
+      <c r="C452" s="129" t="s">
         <v>28</v>
       </c>
-      <c r="D452" s="120"/>
-      <c r="E452" s="120"/>
-      <c r="F452" s="120"/>
-      <c r="G452" s="120"/>
-      <c r="H452" s="120"/>
-      <c r="I452" s="120"/>
+      <c r="D452" s="130"/>
+      <c r="E452" s="130"/>
+      <c r="F452" s="130"/>
+      <c r="G452" s="130"/>
+      <c r="H452" s="130"/>
+      <c r="I452" s="130"/>
       <c r="J452" s="9"/>
       <c r="K452" s="9"/>
       <c r="L452" s="9"/>
@@ -23078,15 +25580,15 @@
       <c r="B453" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C453" s="119" t="s">
+      <c r="C453" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D453" s="120"/>
-      <c r="E453" s="120"/>
-      <c r="F453" s="120"/>
-      <c r="G453" s="120"/>
-      <c r="H453" s="120"/>
-      <c r="I453" s="120"/>
+      <c r="D453" s="130"/>
+      <c r="E453" s="130"/>
+      <c r="F453" s="130"/>
+      <c r="G453" s="130"/>
+      <c r="H453" s="130"/>
+      <c r="I453" s="130"/>
       <c r="J453" s="9"/>
       <c r="K453" s="9"/>
       <c r="L453" s="9"/>
@@ -23102,15 +25604,15 @@
       <c r="B454" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C454" s="119" t="s">
+      <c r="C454" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="D454" s="120"/>
-      <c r="E454" s="120"/>
-      <c r="F454" s="120"/>
-      <c r="G454" s="120"/>
-      <c r="H454" s="120"/>
-      <c r="I454" s="120"/>
+      <c r="D454" s="130"/>
+      <c r="E454" s="130"/>
+      <c r="F454" s="130"/>
+      <c r="G454" s="130"/>
+      <c r="H454" s="130"/>
+      <c r="I454" s="130"/>
       <c r="J454" s="9"/>
       <c r="K454" s="9"/>
       <c r="L454" s="9"/>
@@ -23126,15 +25628,15 @@
       <c r="B455" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C455" s="119" t="s">
+      <c r="C455" s="129" t="s">
         <v>37</v>
       </c>
-      <c r="D455" s="120"/>
-      <c r="E455" s="120"/>
-      <c r="F455" s="120"/>
-      <c r="G455" s="120"/>
-      <c r="H455" s="120"/>
-      <c r="I455" s="120"/>
+      <c r="D455" s="130"/>
+      <c r="E455" s="130"/>
+      <c r="F455" s="130"/>
+      <c r="G455" s="130"/>
+      <c r="H455" s="130"/>
+      <c r="I455" s="130"/>
       <c r="J455" s="9"/>
       <c r="K455" s="9"/>
       <c r="L455" s="9"/>
@@ -23150,15 +25652,15 @@
       <c r="B456" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="C456" s="125" t="s">
+      <c r="C456" s="135" t="s">
         <v>40</v>
       </c>
-      <c r="D456" s="126"/>
-      <c r="E456" s="126"/>
-      <c r="F456" s="126"/>
-      <c r="G456" s="126"/>
-      <c r="H456" s="126"/>
-      <c r="I456" s="126"/>
+      <c r="D456" s="136"/>
+      <c r="E456" s="136"/>
+      <c r="F456" s="136"/>
+      <c r="G456" s="136"/>
+      <c r="H456" s="136"/>
+      <c r="I456" s="136"/>
       <c r="J456" s="27"/>
       <c r="K456" s="27"/>
       <c r="L456" s="27"/>
@@ -24721,15 +27223,15 @@
       <c r="B505" s="30" t="s">
         <v>432</v>
       </c>
-      <c r="C505" s="123" t="s">
+      <c r="C505" s="133" t="s">
         <v>433</v>
       </c>
-      <c r="D505" s="124"/>
-      <c r="E505" s="124"/>
-      <c r="F505" s="124"/>
-      <c r="G505" s="124"/>
-      <c r="H505" s="124"/>
-      <c r="I505" s="124"/>
+      <c r="D505" s="134"/>
+      <c r="E505" s="134"/>
+      <c r="F505" s="134"/>
+      <c r="G505" s="134"/>
+      <c r="H505" s="134"/>
+      <c r="I505" s="134"/>
       <c r="J505" s="9"/>
       <c r="K505" s="29"/>
       <c r="L505" s="9"/>
@@ -24745,15 +27247,15 @@
       <c r="B506" s="30" t="s">
         <v>435</v>
       </c>
-      <c r="C506" s="123" t="s">
+      <c r="C506" s="133" t="s">
         <v>436</v>
       </c>
-      <c r="D506" s="124"/>
-      <c r="E506" s="124"/>
-      <c r="F506" s="124"/>
-      <c r="G506" s="124"/>
-      <c r="H506" s="124"/>
-      <c r="I506" s="124"/>
+      <c r="D506" s="134"/>
+      <c r="E506" s="134"/>
+      <c r="F506" s="134"/>
+      <c r="G506" s="134"/>
+      <c r="H506" s="134"/>
+      <c r="I506" s="134"/>
       <c r="J506" s="9"/>
       <c r="K506" s="29"/>
       <c r="L506" s="9"/>
@@ -24915,15 +27417,15 @@
       <c r="B512" s="30" t="s">
         <v>454</v>
       </c>
-      <c r="C512" s="123" t="s">
+      <c r="C512" s="133" t="s">
         <v>455</v>
       </c>
-      <c r="D512" s="124"/>
-      <c r="E512" s="124"/>
-      <c r="F512" s="124"/>
-      <c r="G512" s="124"/>
-      <c r="H512" s="124"/>
-      <c r="I512" s="124"/>
+      <c r="D512" s="134"/>
+      <c r="E512" s="134"/>
+      <c r="F512" s="134"/>
+      <c r="G512" s="134"/>
+      <c r="H512" s="134"/>
+      <c r="I512" s="134"/>
       <c r="J512" s="9"/>
       <c r="K512" s="29"/>
       <c r="L512" s="9"/>
@@ -25360,14 +27862,14 @@
       <c r="E528" s="54"/>
       <c r="F528" s="54"/>
       <c r="G528" s="54"/>
-      <c r="H528" s="121"/>
-      <c r="I528" s="122"/>
-      <c r="J528" s="122"/>
-      <c r="K528" s="122"/>
-      <c r="L528" s="122"/>
-      <c r="M528" s="122"/>
-      <c r="N528" s="122"/>
-      <c r="O528" s="122"/>
+      <c r="H528" s="131"/>
+      <c r="I528" s="132"/>
+      <c r="J528" s="132"/>
+      <c r="K528" s="132"/>
+      <c r="L528" s="132"/>
+      <c r="M528" s="132"/>
+      <c r="N528" s="132"/>
+      <c r="O528" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -25415,6 +27917,137 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" customWidth="1"/>
+    <col min="4" max="4" width="22.88671875" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="106" t="s">
+        <v>814</v>
+      </c>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+    </row>
+    <row r="2" spans="1:6" s="77" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="100" t="s">
+        <v>815</v>
+      </c>
+      <c r="B2" s="137" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2" s="138"/>
+      <c r="D2" s="100" t="s">
+        <v>758</v>
+      </c>
+      <c r="E2" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="100">
+        <v>1</v>
+      </c>
+      <c r="B3" s="119" t="s">
+        <v>832</v>
+      </c>
+      <c r="C3" s="121"/>
+      <c r="D3" s="75" t="s">
+        <v>934</v>
+      </c>
+      <c r="E3" s="100" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="70">
+        <f>B8</f>
+        <v>1885.3745000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="100" t="s">
+        <v>831</v>
+      </c>
+      <c r="B5" s="100" t="s">
+        <v>821</v>
+      </c>
+      <c r="C5" s="114"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="100">
+        <v>1</v>
+      </c>
+      <c r="B6" s="70">
+        <v>905.8</v>
+      </c>
+      <c r="C6" s="114"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="100" t="s">
+        <v>933</v>
+      </c>
+      <c r="B7" s="70">
+        <f>639.11*2.95</f>
+        <v>1885.3745000000001</v>
+      </c>
+      <c r="C7" s="114"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="115"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="101" t="s">
+        <v>828</v>
+      </c>
+      <c r="B8" s="70">
+        <f>SUM(B7:B7)</f>
+        <v>1885.3745000000001</v>
+      </c>
+      <c r="C8" s="114"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C5:F8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист5"/>
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -25429,23 +28062,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="106" t="s">
         <v>814</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
     </row>
     <row r="2" spans="1:6" s="77" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="76" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="137" t="s">
         <v>816</v>
       </c>
-      <c r="C2" s="128"/>
+      <c r="C2" s="138"/>
       <c r="D2" s="76" t="s">
         <v>758</v>
       </c>
@@ -25460,10 +28093,10 @@
       <c r="A3" s="68">
         <v>1</v>
       </c>
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="119" t="s">
         <v>832</v>
       </c>
-      <c r="C3" s="111"/>
+      <c r="C3" s="121"/>
       <c r="D3" s="75" t="s">
         <v>834</v>
       </c>
@@ -25476,12 +28109,12 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="103"/>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
     </row>
     <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="68" t="s">
@@ -25490,10 +28123,10 @@
       <c r="B5" s="68" t="s">
         <v>821</v>
       </c>
-      <c r="C5" s="104"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
     </row>
     <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="68">
@@ -25502,10 +28135,10 @@
       <c r="B6" s="70">
         <v>806</v>
       </c>
-      <c r="C6" s="104"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="105"/>
+      <c r="C6" s="114"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
     </row>
     <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="68">
@@ -25514,10 +28147,10 @@
       <c r="B7" s="70">
         <v>788.8</v>
       </c>
-      <c r="C7" s="104"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="115"/>
     </row>
     <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="74" t="s">
@@ -25527,10 +28160,10 @@
         <f>SUM(B6:B7)</f>
         <v>1594.8</v>
       </c>
-      <c r="C8" s="104"/>
-      <c r="D8" s="105"/>
-      <c r="E8" s="105"/>
-      <c r="F8" s="105"/>
+      <c r="C8" s="114"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -25542,205 +28175,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="43.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="56.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="56" t="s">
-        <v>757</v>
-      </c>
-      <c r="D1" s="60" t="s">
-        <v>758</v>
-      </c>
-      <c r="E1" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="60" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.3">
-      <c r="A2" s="42">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="D2" s="57" t="s">
-        <v>759</v>
-      </c>
-      <c r="E2" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="59">
-        <v>382.23900000000003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="42">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="59">
-        <v>12.4245</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="42">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="8">
-        <v>30.492000000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" s="42">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="8">
-        <v>4.0179999999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="42">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="8">
-        <v>150.52799999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" s="42">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="8">
-        <v>15.617000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="54" x14ac:dyDescent="0.3">
-      <c r="A8" s="42">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="8">
-        <v>18.769500000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" s="42">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="8">
-        <v>5.3835000000000006</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>